--- a/NPS - matriz-novaiguacu.xlsx
+++ b/NPS - matriz-novaiguacu.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="396">
   <si>
     <t>userId</t>
   </si>
@@ -31,6 +31,9 @@
     <t>userEmail</t>
   </si>
   <si>
+    <t>tipoRespondente</t>
+  </si>
+  <si>
     <t>answeredAt</t>
   </si>
   <si>
@@ -88,19 +91,190 @@
     <t>AÇÃO</t>
   </si>
   <si>
-    <t>Última atualização: 22/03/2026 16:30</t>
+    <t>Última atualização: 25/03/2026 18:31</t>
+  </si>
+  <si>
+    <t>62261c5768ca0d001c229386</t>
+  </si>
+  <si>
+    <t>69b86aba3648364cda618874</t>
+  </si>
+  <si>
+    <t>Queremos ouvir a sua opinião</t>
+  </si>
+  <si>
+    <t>matriz-novaiguacu</t>
+  </si>
+  <si>
+    <t>MARQUIASIO PAULIQUEVIS</t>
+  </si>
+  <si>
+    <t>pauliquevismarquiasio@gmail.com</t>
+  </si>
+  <si>
+    <t>responsavel</t>
+  </si>
+  <si>
+    <t>2026-03-25T20:30:30.073Z</t>
+  </si>
+  <si>
+    <t>10 - Extremamente provável</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eu acho que o ensino é maravilhoso </t>
+  </si>
+  <si>
+    <t>6 - Muito Satisfeito</t>
+  </si>
+  <si>
+    <t>1 - Muito Insatisfeito</t>
+  </si>
+  <si>
+    <t>Responsável</t>
+  </si>
+  <si>
+    <t>Promotor</t>
+  </si>
+  <si>
+    <t>6785ab10f184ec03d2c8a748</t>
+  </si>
+  <si>
+    <t>ROGERIO SILVA DE ANDRADE</t>
+  </si>
+  <si>
+    <t>oliveirakarsilva@yahoo.com.br</t>
+  </si>
+  <si>
+    <t>2026-03-25T20:23:15.996Z</t>
+  </si>
+  <si>
+    <t>Gosto dos Gestores , responsáveis pelo Ensino Médio Militar de N. Iguaçu.
+Sempre atende aos responsáveis com atenção.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Os professores poderiam ter conteúdos mais dinâmicos.
+Vejo muita dificuldade  de aprendizados com as  interpretação de questões .
+Acho que poderiam elaborar algo que ajudasse os alunos.
+</t>
+  </si>
+  <si>
+    <t>Neutro</t>
+  </si>
+  <si>
+    <t>677bc2375316897914c5b776</t>
+  </si>
+  <si>
+    <t>ALDENI TOMAZ FERREIRA</t>
+  </si>
+  <si>
+    <t>niniferreira2024@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-25T19:59:40.311Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O ensino em si é bom, mas tem pontos a melhorar </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estrutura do banheiro" portas quebras"
+Alunos não poderem usar o elevador </t>
+  </si>
+  <si>
+    <t>697bbf8f2dd633ec474a0f62</t>
+  </si>
+  <si>
+    <t>MILENE CIPRIANO FERREIRA</t>
+  </si>
+  <si>
+    <t>milenesipliane@yahoo.com.br</t>
+  </si>
+  <si>
+    <t>2026-03-25T01:24:46.405Z</t>
+  </si>
+  <si>
+    <t>Equipe e professores excelentes</t>
+  </si>
+  <si>
+    <t>6989f4f34d2df57ae066e568</t>
+  </si>
+  <si>
+    <t>AMANDA SOARES RODRIGUES DOS SANTOS</t>
+  </si>
+  <si>
+    <t>amandasantos.ni34@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-25T00:31:46.045Z</t>
+  </si>
+  <si>
+    <t>Primeira experiência com q escola, ainda não conheço muito bem</t>
+  </si>
+  <si>
+    <t>633e0945a58df4001d6a7359</t>
+  </si>
+  <si>
+    <t>69b898af21c08e4e2e112204</t>
+  </si>
+  <si>
+    <t>LUAN RAPHAEL DA ROCHA TAVARES</t>
+  </si>
+  <si>
+    <t>luanmt22088918@matrizeducacao.com.br</t>
+  </si>
+  <si>
+    <t>estudante</t>
+  </si>
+  <si>
+    <t>2026-03-24T20:58:30.857Z</t>
+  </si>
+  <si>
+    <t>satisfação em alguns pontos, mas não todos</t>
+  </si>
+  <si>
+    <t>abaixem os preços na cantina, está tudo um absurdo que é incomparável aos preços dos mesmos produtos fora da escola</t>
+  </si>
+  <si>
+    <t>Aluno</t>
+  </si>
+  <si>
+    <t>69658cd4c2a9c98a06e28079</t>
+  </si>
+  <si>
+    <t>THAYANE VIEIRA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>psithayvieira@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-24T01:52:58.4Z</t>
+  </si>
+  <si>
+    <t>Estou dando essa nota porque estou percebendo o quanto o meu filho tem se dedicado aos estudos e se sente pertencente a escola. Principalmente pelos colegas de escola.</t>
+  </si>
+  <si>
+    <t>Me filho está gostando da escola, é o primeiro ano dele nesta escola. Acredito que essa instituição tem muito a agregar na vida dele.</t>
+  </si>
+  <si>
+    <t>6984e946f11540ff63c19a68</t>
+  </si>
+  <si>
+    <t>CLAUDIA GISELE AZEVEDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>cacagisa123@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-23T14:13:14.732Z</t>
+  </si>
+  <si>
+    <t>Estou bem satisfeita com escola .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Só tenho um questionamento sobre a questão que pedi pra conversar com a parte pedagógica sobre as questões emocionais da Ingrid e ficaram de marcar pra conversarmos e não fui notificada a ir pra essa conversa . 
+</t>
   </si>
   <si>
     <t>693222776b0fec95f75c2475</t>
-  </si>
-  <si>
-    <t>69b898af21c08e4e2e112204</t>
-  </si>
-  <si>
-    <t>Queremos ouvir a sua opinião</t>
-  </si>
-  <si>
-    <t>matriz-novaiguacu</t>
   </si>
   <si>
     <t>PEDRO GONÇALVES LOBO</t>
@@ -116,21 +290,9 @@
 </t>
   </si>
   <si>
-    <t>6 - Muito Satisfeito</t>
-  </si>
-  <si>
-    <t>Aluno</t>
-  </si>
-  <si>
-    <t>Neutro</t>
-  </si>
-  <si>
     <t>698b56f7651157cae001f2fa</t>
   </si>
   <si>
-    <t>69b86aba3648364cda618874</t>
-  </si>
-  <si>
     <t>MELL NATHALIE DA ROCHA SPRENGER</t>
   </si>
   <si>
@@ -143,15 +305,9 @@
     <t>Boa estrutura e bom ensino, porém os alunos novos ficam um pouco perdidos e sem muita atenção.</t>
   </si>
   <si>
-    <t>1 - Muito Insatisfeito</t>
-  </si>
-  <si>
     <t>A coordenação infelizmente acaba recebendo os alunos de maneira rude e não dão a devida importância às suas questões.</t>
   </si>
   <si>
-    <t>Responsável</t>
-  </si>
-  <si>
     <t>688961f791d4dead99310e2f</t>
   </si>
   <si>
@@ -164,13 +320,7 @@
     <t>2026-03-22T03:03:47.245Z</t>
   </si>
   <si>
-    <t>10 - Extremamente provável</t>
-  </si>
-  <si>
     <t xml:space="preserve">O cuidado com o aluno, e as formas únicas de </t>
-  </si>
-  <si>
-    <t>Promotor</t>
   </si>
   <si>
     <t>698b56f76511577fe701f2ee</t>
@@ -1362,26 +1512,27 @@
     <col customWidth="1" min="4" max="4" width="14.25"/>
     <col customWidth="1" min="5" max="5" width="42.88"/>
     <col customWidth="1" min="6" max="6" width="35.38"/>
-    <col customWidth="1" min="7" max="7" width="20.5"/>
-    <col customWidth="1" min="8" max="8" width="68.0"/>
-    <col customWidth="1" min="9" max="9" width="309.63"/>
-    <col customWidth="1" min="10" max="10" width="67.63"/>
-    <col customWidth="1" min="11" max="11" width="71.63"/>
-    <col customWidth="1" min="12" max="12" width="74.13"/>
-    <col customWidth="1" min="13" max="13" width="49.25"/>
-    <col customWidth="1" min="14" max="14" width="69.88"/>
-    <col customWidth="1" min="15" max="15" width="35.63"/>
-    <col customWidth="1" min="16" max="16" width="50.25"/>
-    <col customWidth="1" min="17" max="17" width="69.38"/>
-    <col customWidth="1" min="18" max="18" width="62.0"/>
-    <col customWidth="1" min="19" max="19" width="831.5"/>
-    <col customWidth="1" min="20" max="20" width="14.25"/>
-    <col customWidth="1" min="21" max="21" width="7.75"/>
-    <col customWidth="1" min="22" max="22" width="12.75"/>
-    <col customWidth="1" min="23" max="23" width="24.13"/>
-    <col customWidth="1" min="24" max="24" width="16.38"/>
-    <col customWidth="1" min="25" max="25" width="5.25"/>
-    <col customWidth="1" min="26" max="26" width="28.63"/>
+    <col customWidth="1" min="7" max="7" width="13.38"/>
+    <col customWidth="1" min="8" max="8" width="20.5"/>
+    <col customWidth="1" min="9" max="9" width="68.0"/>
+    <col customWidth="1" min="10" max="10" width="309.63"/>
+    <col customWidth="1" min="11" max="11" width="67.63"/>
+    <col customWidth="1" min="12" max="12" width="71.63"/>
+    <col customWidth="1" min="13" max="13" width="74.13"/>
+    <col customWidth="1" min="14" max="14" width="49.25"/>
+    <col customWidth="1" min="15" max="15" width="69.88"/>
+    <col customWidth="1" min="16" max="16" width="35.63"/>
+    <col customWidth="1" min="17" max="17" width="50.25"/>
+    <col customWidth="1" min="18" max="18" width="69.38"/>
+    <col customWidth="1" min="19" max="19" width="62.0"/>
+    <col customWidth="1" min="20" max="20" width="831.5"/>
+    <col customWidth="1" min="21" max="21" width="14.25"/>
+    <col customWidth="1" min="22" max="22" width="7.75"/>
+    <col customWidth="1" min="23" max="23" width="12.75"/>
+    <col customWidth="1" min="24" max="24" width="24.13"/>
+    <col customWidth="1" min="25" max="25" width="16.38"/>
+    <col customWidth="1" min="26" max="26" width="5.25"/>
+    <col customWidth="1" min="27" max="27" width="28.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1463,311 +1614,328 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2" s="2">
-        <v>7.0</v>
+        <v>33</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K2" s="2">
-        <v>5.0</v>
+        <v>36</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q2" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R2" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2" t="s">
-        <v>35</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T2" s="2"/>
       <c r="U2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V2" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
+      <c r="AA2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I3" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K3" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N3" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O3" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P3" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R3" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="S3" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="U3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H3" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J3" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L3" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N3" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O3" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q3" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="R3" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V3" s="3"/>
+      <c r="V3" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
       <c r="Y3" s="3"/>
       <c r="Z3" s="3"/>
+      <c r="AA3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I4" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K4" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L4" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="M4" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N4" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="O4" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="P4" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="R4" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="V4" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N4" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="U4" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V4" s="3"/>
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="J5" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="K5" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L5" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M5" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N5" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O5" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P5" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="Q5" s="2">
-        <v>4.0</v>
+        <v>35</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="R5" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2" t="s">
-        <v>45</v>
-      </c>
+        <v>4.0</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T5" s="2"/>
       <c r="U5" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V5" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
+      <c r="AA5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I6" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="J6" s="2">
-        <v>5.0</v>
+      <c r="I6" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="K6" s="2">
         <v>5.0</v>
@@ -1776,215 +1944,224 @@
         <v>5.0</v>
       </c>
       <c r="M6" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="N6" s="2">
         <v>5.0</v>
       </c>
-      <c r="O6" s="2">
-        <v>5.0</v>
+      <c r="O6" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P6" s="2">
         <v>5.0</v>
       </c>
-      <c r="Q6" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R6" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S6" s="2"/>
-      <c r="T6" s="2" t="s">
-        <v>45</v>
-      </c>
+      <c r="Q6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T6" s="2"/>
       <c r="U6" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V6" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="V6" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
+      <c r="AA6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I7" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L7" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="M7" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N7" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O7" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P7" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="R7" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="H7" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="J7" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="K7" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L7" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M7" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N7" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O7" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q7" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R7" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>68</v>
+      <c r="S7" s="2">
+        <v>4.0</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V7" s="3"/>
+        <v>72</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
       <c r="Y7" s="3"/>
       <c r="Z7" s="3"/>
+      <c r="AA7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H8" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>73</v>
+        <v>33</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I8" s="2">
+        <v>9.0</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="L8" s="2">
+        <v>5.0</v>
       </c>
       <c r="M8" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="O8" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
+      </c>
+      <c r="N8" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P8" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="Q8" s="2">
-        <v>5.0</v>
+        <v>5.0</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V8" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
+      <c r="AA8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H9" s="2">
-        <v>8.0</v>
+        <v>33</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="J9" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="K9" s="2">
-        <v>5.0</v>
+        <v>35</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="L9" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="M9" s="2">
-        <v>5.0</v>
+        <v>5.0</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="N9" s="2">
         <v>5.0</v>
@@ -1993,348 +2170,363 @@
         <v>5.0</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q9" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="R9" s="2">
-        <v>5.0</v>
+        <v>37</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V9" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
+      <c r="AA9" s="3"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
+      </c>
+      <c r="I10" s="2">
+        <v>7.0</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="L10" s="2">
+        <v>5.0</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="P10" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="Q10" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2" t="s">
-        <v>45</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R10" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S10" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T10" s="2"/>
       <c r="U10" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V10" s="3"/>
+        <v>72</v>
+      </c>
+      <c r="V10" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
+      <c r="AA10" s="3"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I11" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K11" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="L11" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H11" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>34</v>
+      <c r="M11" s="2">
+        <v>4.0</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="O11" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P11" s="2">
+        <v>4.0</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="S11" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="R11" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="S11" s="2">
+        <v>5.0</v>
+      </c>
       <c r="T11" s="2" t="s">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V11" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="V11" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>92</v>
+        <v>33</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>93</v>
+        <v>35</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="O12" s="2">
+        <v>4.0</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="S12" s="2"/>
-      <c r="T12" s="2" t="s">
-        <v>45</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T12" s="2"/>
       <c r="U12" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V12" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="V12" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
+      <c r="AA12" s="3"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H13" s="2">
-        <v>5.0</v>
+        <v>33</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J13" s="2">
-        <v>4.0</v>
+        <v>35</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>105</v>
       </c>
       <c r="K13" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="L13" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="M13" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="N13" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="O13" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="P13" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="Q13" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="R13" s="2">
         <v>4.0</v>
       </c>
-      <c r="S13" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="T13" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="S13" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T13" s="2"/>
       <c r="U13" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="V13" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="V13" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="W13" s="3"/>
       <c r="X13" s="3"/>
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
+      <c r="AA13" s="3"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>104</v>
+        <v>33</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>50</v>
+        <v>109</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>105</v>
+        <v>35</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>34</v>
+        <v>110</v>
+      </c>
+      <c r="K14" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L14" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M14" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N14" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="O14" s="2">
+        <v>5.0</v>
       </c>
       <c r="P14" s="2">
         <v>5.0</v>
@@ -2342,1575 +2534,1644 @@
       <c r="Q14" s="2">
         <v>5.0</v>
       </c>
-      <c r="R14" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="S14" s="2"/>
-      <c r="T14" s="2" t="s">
-        <v>45</v>
-      </c>
+      <c r="R14" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S14" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T14" s="2"/>
       <c r="U14" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V14" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="V14" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="W14" s="3"/>
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
+      <c r="AA14" s="3"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I15" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="K15" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L15" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M15" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N15" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O15" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P15" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q15" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="S15" s="2"/>
+      <c r="R15" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S15" s="2">
+        <v>5.0</v>
+      </c>
       <c r="T15" s="2" t="s">
-        <v>45</v>
+        <v>116</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V15" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="V15" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="W15" s="3"/>
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
+      <c r="AA15" s="3"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>114</v>
+        <v>68</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>115</v>
+        <v>120</v>
+      </c>
+      <c r="I16" s="2">
+        <v>8.0</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>34</v>
+        <v>121</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="N16" s="2">
+        <v>4.0</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="S16" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="P16" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="R16" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="T16" s="2" t="s">
-        <v>45</v>
+        <v>122</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V16" s="3"/>
+        <v>72</v>
+      </c>
+      <c r="V16" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="H17" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>120</v>
+        <v>33</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I17" s="2">
+        <v>8.0</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>34</v>
+        <v>122</v>
       </c>
       <c r="K17" s="2">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="L17" s="2">
         <v>5.0</v>
       </c>
       <c r="M17" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="N17" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="O17" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q17" s="2">
-        <v>5.0</v>
+        <v>5.0</v>
+      </c>
+      <c r="P17" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="R17" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="S17" s="2" t="s">
-        <v>121</v>
+        <v>4.0</v>
+      </c>
+      <c r="S17" s="2">
+        <v>5.0</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>35</v>
+        <v>122</v>
       </c>
       <c r="U17" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="V17" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="V17" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="W17" s="3"/>
       <c r="X17" s="3"/>
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
+      <c r="AA17" s="3"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H18" s="2">
-        <v>8.0</v>
+        <v>33</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>130</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="J18" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="K18" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L18" s="2">
-        <v>5.0</v>
+        <v>35</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="O18" s="2">
-        <v>5.0</v>
+        <v>37</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q18" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R18" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="S18" s="2"/>
-      <c r="T18" s="2" t="s">
-        <v>45</v>
-      </c>
+        <v>4.0</v>
+      </c>
+      <c r="R18" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T18" s="2"/>
       <c r="U18" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V18" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="V18" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="W18" s="3"/>
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
+      <c r="AA18" s="3"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>130</v>
+        <v>33</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
+      </c>
+      <c r="I19" s="2">
+        <v>9.0</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>34</v>
+        <v>136</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="R19" s="2">
-        <v>3.0</v>
+        <v>37</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="T19" s="2" t="s">
-        <v>45</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="T19" s="2"/>
       <c r="U19" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V19" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="V19" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H20" s="2">
-        <v>8.0</v>
+        <v>33</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>140</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="J20" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="K20" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L20" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M20" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N20" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O20" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P20" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q20" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R20" s="2">
-        <v>5.0</v>
+        <v>35</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="T20" s="2" t="s">
-        <v>35</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="T20" s="2"/>
       <c r="U20" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V20" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="V20" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="W20" s="3"/>
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
       <c r="Z20" s="3"/>
+      <c r="AA20" s="3"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="H21" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>143</v>
+        <v>68</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="I21" s="2">
+        <v>5.0</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>34</v>
+        <v>146</v>
+      </c>
+      <c r="K21" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="L21" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="M21" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N21" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="O21" s="2">
+        <v>3.0</v>
       </c>
       <c r="P21" s="2">
         <v>3.0</v>
       </c>
       <c r="Q21" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="R21" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S21" s="2" t="s">
-        <v>144</v>
+        <v>3.0</v>
+      </c>
+      <c r="S21" s="2">
+        <v>4.0</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>35</v>
+        <v>147</v>
       </c>
       <c r="U21" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V21" s="3"/>
+        <v>72</v>
+      </c>
+      <c r="V21" s="2" t="s">
+        <v>148</v>
+      </c>
       <c r="W21" s="3"/>
       <c r="X21" s="3"/>
       <c r="Y21" s="3"/>
       <c r="Z21" s="3"/>
+      <c r="AA21" s="3"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="H22" s="2">
-        <v>7.0</v>
+        <v>33</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>152</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="J22" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="K22" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L22" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M22" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N22" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O22" s="2">
-        <v>5.0</v>
+        <v>35</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="Q22" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="R22" s="2">
         <v>5.0</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="T22" s="2" t="s">
-        <v>45</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="T22" s="2"/>
       <c r="U22" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V22" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="V22" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
       <c r="Y22" s="3"/>
       <c r="Z22" s="3"/>
+      <c r="AA22" s="3"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="H23" s="2">
-        <v>6.0</v>
+        <v>33</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>157</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="J23" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="K23" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="L23" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="M23" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="N23" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="O23" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="P23" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="Q23" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="R23" s="2">
-        <v>4.0</v>
+        <v>35</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="T23" s="2" t="s">
-        <v>45</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="T23" s="2"/>
       <c r="U23" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="V23" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="V23" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="W23" s="3"/>
       <c r="X23" s="3"/>
       <c r="Y23" s="3"/>
       <c r="Z23" s="3"/>
+      <c r="AA23" s="3"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="H24" s="2">
-        <v>8.0</v>
+        <v>33</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>162</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>161</v>
+        <v>35</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K24" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="L24" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="M24" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="N24" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="O24" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="P24" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="Q24" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="R24" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S24" s="2"/>
-      <c r="T24" s="2" t="s">
-        <v>45</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T24" s="2"/>
       <c r="U24" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V24" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="V24" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
       <c r="Z24" s="3"/>
+      <c r="AA24" s="3"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="I25" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L25" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="M25" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N25" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O25" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="P25" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="Q25" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="H25" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="J25" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="K25" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N25" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="O25" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="P25" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="Q25" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="R25" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="S25" s="2" t="s">
-        <v>166</v>
+      <c r="R25" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S25" s="2">
+        <v>2.0</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>45</v>
+        <v>169</v>
       </c>
       <c r="U25" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V25" s="3"/>
+        <v>72</v>
+      </c>
+      <c r="V25" s="2" t="s">
+        <v>148</v>
+      </c>
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
       <c r="Y25" s="3"/>
       <c r="Z25" s="3"/>
+      <c r="AA25" s="3"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="H26" s="2">
+        <v>33</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="I26" s="2">
         <v>8.0</v>
       </c>
-      <c r="I26" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="J26" s="2">
-        <v>5.0</v>
+      <c r="J26" s="2" t="s">
+        <v>174</v>
       </c>
       <c r="K26" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>34</v>
+        <v>5.0</v>
+      </c>
+      <c r="L26" s="2">
+        <v>5.0</v>
       </c>
       <c r="M26" s="2">
         <v>5.0</v>
       </c>
-      <c r="N26" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O26" s="2">
-        <v>5.0</v>
+      <c r="N26" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P26" s="2">
         <v>5.0</v>
       </c>
-      <c r="Q26" s="2">
-        <v>4.0</v>
+      <c r="Q26" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="R26" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="S26" s="2"/>
-      <c r="T26" s="2" t="s">
-        <v>45</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="S26" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T26" s="2"/>
       <c r="U26" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V26" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="V26" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
       <c r="Y26" s="3"/>
       <c r="Z26" s="3"/>
+      <c r="AA26" s="3"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="H27" s="2">
-        <v>9.0</v>
+        <v>33</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>178</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="J27" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="K27" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L27" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M27" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N27" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O27" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P27" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q27" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R27" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S27" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q27" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S27" s="2">
+        <v>3.0</v>
+      </c>
       <c r="T27" s="2" t="s">
-        <v>45</v>
+        <v>180</v>
       </c>
       <c r="U27" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V27" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="V27" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="W27" s="3"/>
       <c r="X27" s="3"/>
       <c r="Y27" s="3"/>
       <c r="Z27" s="3"/>
+      <c r="AA27" s="3"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
+      </c>
+      <c r="I28" s="2">
+        <v>8.0</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N28" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="O28" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="P28" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q28" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="R28" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="S28" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
+      </c>
+      <c r="K28" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L28" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M28" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N28" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O28" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P28" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q28" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R28" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S28" s="2">
+        <v>5.0</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>45</v>
+        <v>186</v>
       </c>
       <c r="U28" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V28" s="3"/>
+        <v>72</v>
+      </c>
+      <c r="V28" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
       <c r="Z28" s="3"/>
+      <c r="AA28" s="3"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="H29" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="J29" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="K29" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L29" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M29" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N29" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O29" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P29" s="2">
-        <v>5.0</v>
+        <v>68</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="I29" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O29" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="Q29" s="2">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="R29" s="2">
         <v>5.0</v>
       </c>
-      <c r="S29" s="2"/>
+      <c r="S29" s="2">
+        <v>5.0</v>
+      </c>
       <c r="T29" s="2" t="s">
-        <v>45</v>
+        <v>192</v>
       </c>
       <c r="U29" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V29" s="3"/>
+        <v>72</v>
+      </c>
+      <c r="V29" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
       <c r="Y29" s="3"/>
       <c r="Z29" s="3"/>
+      <c r="AA29" s="3"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="I30" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="K30" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L30" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M30" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N30" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O30" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P30" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q30" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="H30" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L30" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M30" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N30" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O30" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="P30" s="2">
+      <c r="R30" s="2">
         <v>3.0</v>
       </c>
-      <c r="Q30" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="R30" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S30" s="2" t="s">
-        <v>193</v>
+      <c r="S30" s="2">
+        <v>5.0</v>
       </c>
       <c r="T30" s="2" t="s">
-        <v>45</v>
+        <v>198</v>
       </c>
       <c r="U30" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V30" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="V30" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
       <c r="Y30" s="3"/>
       <c r="Z30" s="3"/>
+      <c r="AA30" s="3"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>197</v>
+        <v>33</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
+      </c>
+      <c r="I31" s="2">
+        <v>6.0</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>34</v>
+        <v>203</v>
       </c>
       <c r="K31" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M31" s="2" t="s">
-        <v>34</v>
+        <v>4.0</v>
+      </c>
+      <c r="L31" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="M31" s="2">
+        <v>4.0</v>
       </c>
       <c r="N31" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O31" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="P31" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q31" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="R31" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="S31" s="2" t="s">
-        <v>199</v>
+        <v>4.0</v>
+      </c>
+      <c r="O31" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="P31" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="Q31" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="R31" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="S31" s="2">
+        <v>4.0</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>35</v>
+        <v>204</v>
       </c>
       <c r="U31" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V31" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="V31" s="2" t="s">
+        <v>148</v>
+      </c>
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
       <c r="Y31" s="3"/>
       <c r="Z31" s="3"/>
+      <c r="AA31" s="3"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>203</v>
+        <v>33</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
+      </c>
+      <c r="I32" s="2">
+        <v>8.0</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>34</v>
+        <v>209</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N32" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="O32" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="L32" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="M32" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="N32" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="O32" s="2">
+        <v>2.0</v>
       </c>
       <c r="P32" s="2">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q32" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="R32" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S32" s="2"/>
-      <c r="T32" s="2" t="s">
-        <v>45</v>
-      </c>
+        <v>4.0</v>
+      </c>
+      <c r="S32" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T32" s="2"/>
       <c r="U32" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V32" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="V32" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="W32" s="3"/>
       <c r="X32" s="3"/>
       <c r="Y32" s="3"/>
       <c r="Z32" s="3"/>
+      <c r="AA32" s="3"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="H33" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="J33" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="I33" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="K33" s="2">
+        <v>5.0</v>
       </c>
       <c r="L33" s="2">
         <v>4.0</v>
       </c>
-      <c r="M33" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N33" s="2">
-        <v>5.0</v>
+      <c r="M33" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N33" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P33" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
+      </c>
+      <c r="P33" s="2">
+        <v>4.0</v>
       </c>
       <c r="Q33" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="R33" s="2">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="S33" s="2" t="s">
-        <v>210</v>
+        <v>37</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>35</v>
+        <v>214</v>
       </c>
       <c r="U33" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="V33" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="V33" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="W33" s="3"/>
       <c r="X33" s="3"/>
       <c r="Y33" s="3"/>
       <c r="Z33" s="3"/>
+      <c r="AA33" s="3"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="H34" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="J34" s="2">
-        <v>5.0</v>
+        <v>33</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="I34" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>219</v>
       </c>
       <c r="K34" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="L34" s="2">
         <v>3.0</v>
       </c>
-      <c r="M34" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="N34" s="2" t="s">
-        <v>34</v>
+      <c r="M34" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N34" s="2">
+        <v>5.0</v>
       </c>
       <c r="O34" s="2">
         <v>5.0</v>
       </c>
-      <c r="P34" s="2" t="s">
-        <v>43</v>
+      <c r="P34" s="2">
+        <v>5.0</v>
       </c>
       <c r="Q34" s="2">
         <v>5.0</v>
       </c>
       <c r="R34" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S34" s="2"/>
-      <c r="T34" s="2" t="s">
-        <v>35</v>
-      </c>
+        <v>4.0</v>
+      </c>
+      <c r="S34" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="T34" s="2"/>
       <c r="U34" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V34" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="V34" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
       <c r="Z34" s="3"/>
+      <c r="AA34" s="3"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="H35" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>220</v>
+        <v>33</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="I35" s="2">
+        <v>9.0</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>34</v>
+        <v>224</v>
       </c>
       <c r="K35" s="2">
         <v>5.0</v>
       </c>
-      <c r="L35" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M35" s="2" t="s">
-        <v>34</v>
+      <c r="L35" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M35" s="2">
+        <v>5.0</v>
       </c>
       <c r="N35" s="2">
         <v>5.0</v>
       </c>
       <c r="O35" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="P35" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="Q35" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="R35" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="S35" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="T35" s="2" t="s">
-        <v>35</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="S35" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T35" s="2"/>
       <c r="U35" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V35" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="V35" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="W35" s="3"/>
       <c r="X35" s="3"/>
       <c r="Y35" s="3"/>
       <c r="Z35" s="3"/>
+      <c r="AA35" s="3"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>225</v>
+        <v>33</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>50</v>
+        <v>228</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="J36" s="2">
-        <v>5.0</v>
+        <v>35</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>229</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M36" s="2">
-        <v>5.0</v>
+        <v>37</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q36" s="2">
-        <v>4.0</v>
+        <v>37</v>
+      </c>
+      <c r="Q36" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="S36" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="S36" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="T36" s="2" t="s">
-        <v>35</v>
+        <v>230</v>
       </c>
       <c r="U36" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V36" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="V36" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="W36" s="3"/>
       <c r="X36" s="3"/>
       <c r="Y36" s="3"/>
       <c r="Z36" s="3"/>
+      <c r="AA36" s="3"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="H37" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="J37" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="K37" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="I37" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="K37" s="2">
+        <v>5.0</v>
       </c>
       <c r="L37" s="2">
         <v>5.0</v>
@@ -3918,220 +4179,231 @@
       <c r="M37" s="2">
         <v>5.0</v>
       </c>
-      <c r="N37" s="2" t="s">
-        <v>34</v>
+      <c r="N37" s="2">
+        <v>5.0</v>
       </c>
       <c r="O37" s="2">
         <v>5.0</v>
       </c>
       <c r="P37" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="Q37" s="2">
         <v>5.0</v>
       </c>
       <c r="R37" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="S37" s="2"/>
-      <c r="T37" s="2" t="s">
-        <v>35</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="S37" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T37" s="2"/>
       <c r="U37" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="V37" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="V37" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="W37" s="3"/>
       <c r="X37" s="3"/>
       <c r="Y37" s="3"/>
       <c r="Z37" s="3"/>
+      <c r="AA37" s="3"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>235</v>
+        <v>33</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
+      </c>
+      <c r="I38" s="2">
+        <v>9.0</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>34</v>
+        <v>240</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="O38" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="O38" s="2">
+        <v>5.0</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q38" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="Q38" s="2">
+        <v>3.0</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="S38" s="2" t="s">
-        <v>237</v>
+        <v>37</v>
+      </c>
+      <c r="S38" s="2">
+        <v>5.0</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>45</v>
+        <v>241</v>
       </c>
       <c r="U38" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V38" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="V38" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="W38" s="3"/>
       <c r="X38" s="3"/>
       <c r="Y38" s="3"/>
       <c r="Z38" s="3"/>
+      <c r="AA38" s="3"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="H39" s="2">
-        <v>6.0</v>
+        <v>68</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="J39" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="K39" s="2">
-        <v>5.0</v>
+        <v>35</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="L39" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O39" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P39" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="Q39" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="R39" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="S39" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="O39" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P39" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q39" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R39" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S39" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="T39" s="2" t="s">
-        <v>45</v>
+        <v>247</v>
       </c>
       <c r="U39" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="V39" s="3"/>
+        <v>72</v>
+      </c>
+      <c r="V39" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
+      <c r="AA39" s="3"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="H40" s="2">
-        <v>9.0</v>
+        <v>33</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>251</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="J40" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="K40" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L40" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M40" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N40" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O40" s="2">
-        <v>5.0</v>
+        <v>35</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N40" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O40" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q40" s="2">
         <v>5.0</v>
@@ -4139,342 +4411,355 @@
       <c r="R40" s="2">
         <v>5.0</v>
       </c>
-      <c r="S40" s="2"/>
-      <c r="T40" s="2" t="s">
-        <v>45</v>
-      </c>
+      <c r="S40" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T40" s="2"/>
       <c r="U40" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V40" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="V40" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
+      <c r="AA40" s="3"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="I41" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="K41" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L41" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="H41" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L41" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="M41" s="2">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="N41" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="O41" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="R41" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="S41" s="2" t="s">
-        <v>253</v>
+        <v>38</v>
+      </c>
+      <c r="R41" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S41" s="2">
+        <v>4.0</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>45</v>
+        <v>258</v>
       </c>
       <c r="U41" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="V41" s="3"/>
+        <v>72</v>
+      </c>
+      <c r="V41" s="2" t="s">
+        <v>148</v>
+      </c>
       <c r="W41" s="3"/>
       <c r="X41" s="3"/>
       <c r="Y41" s="3"/>
       <c r="Z41" s="3"/>
+      <c r="AA41" s="3"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="I42" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="K42" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L42" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="M42" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N42" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P42" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q42" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M42" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N42" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="O42" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="P42" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q42" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="R42" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="S42" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="T42" s="2" t="s">
-        <v>45</v>
-      </c>
+      <c r="R42" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S42" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T42" s="2"/>
       <c r="U42" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V42" s="3"/>
+        <v>72</v>
+      </c>
+      <c r="V42" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
       <c r="Y42" s="3"/>
       <c r="Z42" s="3"/>
+      <c r="AA42" s="3"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>263</v>
+        <v>68</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
+      </c>
+      <c r="I43" s="2">
+        <v>8.0</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>34</v>
+        <v>268</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L43" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="L43" s="2">
+        <v>5.0</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="O43" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="P43" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q43" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="R43" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="S43" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="O43" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P43" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="Q43" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="R43" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="S43" s="2">
+        <v>3.0</v>
+      </c>
       <c r="T43" s="2" t="s">
-        <v>45</v>
+        <v>269</v>
       </c>
       <c r="U43" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V43" s="3"/>
+        <v>72</v>
+      </c>
+      <c r="V43" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="W43" s="3"/>
       <c r="X43" s="3"/>
       <c r="Y43" s="3"/>
       <c r="Z43" s="3"/>
+      <c r="AA43" s="3"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="H44" s="2">
-        <v>8.0</v>
+        <v>68</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="J44" s="2">
-        <v>5.0</v>
+        <v>35</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>274</v>
       </c>
       <c r="K44" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="L44" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="M44" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="N44" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="O44" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P44" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q44" s="2">
-        <v>5.0</v>
+        <v>5.0</v>
+      </c>
+      <c r="O44" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P44" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q44" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="R44" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="S44" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="T44" s="2" t="s">
-        <v>45</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="T44" s="2"/>
       <c r="U44" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V44" s="3"/>
+        <v>72</v>
+      </c>
+      <c r="V44" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="W44" s="3"/>
       <c r="X44" s="3"/>
       <c r="Y44" s="3"/>
       <c r="Z44" s="3"/>
+      <c r="AA44" s="3"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="H45" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="J45" s="2">
-        <v>4.0</v>
+        <v>68</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="I45" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>279</v>
       </c>
       <c r="K45" s="2">
         <v>5.0</v>
       </c>
-      <c r="L45" s="2">
-        <v>5.0</v>
+      <c r="L45" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="M45" s="2">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="N45" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="O45" s="2">
-        <v>5.0</v>
+        <v>5.0</v>
+      </c>
+      <c r="O45" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P45" s="2">
         <v>5.0</v>
@@ -4485,478 +4770,499 @@
       <c r="R45" s="2">
         <v>5.0</v>
       </c>
-      <c r="S45" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="T45" s="2" t="s">
-        <v>45</v>
-      </c>
+      <c r="S45" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="T45" s="2"/>
       <c r="U45" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V45" s="3"/>
+        <v>72</v>
+      </c>
+      <c r="V45" s="2" t="s">
+        <v>148</v>
+      </c>
       <c r="W45" s="3"/>
       <c r="X45" s="3"/>
       <c r="Y45" s="3"/>
       <c r="Z45" s="3"/>
+      <c r="AA45" s="3"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>280</v>
+        <v>33</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>50</v>
+        <v>283</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>281</v>
+        <v>35</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>34</v>
+        <v>284</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q46" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R46" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="S46" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="S46" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="T46" s="2" t="s">
-        <v>45</v>
+        <v>285</v>
       </c>
       <c r="U46" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V46" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="V46" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="W46" s="3"/>
       <c r="X46" s="3"/>
       <c r="Y46" s="3"/>
       <c r="Z46" s="3"/>
+      <c r="AA46" s="3"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="H47" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="J47" s="2">
-        <v>5.0</v>
+        <v>33</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="I47" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>290</v>
       </c>
       <c r="K47" s="2">
         <v>5.0</v>
       </c>
       <c r="L47" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="M47" s="2" t="s">
-        <v>34</v>
+        <v>5.0</v>
+      </c>
+      <c r="M47" s="2">
+        <v>3.0</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="P47" s="2">
-        <v>2.0</v>
+        <v>38</v>
+      </c>
+      <c r="P47" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="Q47" s="2">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="R47" s="2">
         <v>4.0</v>
       </c>
-      <c r="S47" s="2"/>
-      <c r="T47" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="S47" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="T47" s="2"/>
       <c r="U47" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V47" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="V47" s="2" t="s">
+        <v>148</v>
+      </c>
       <c r="W47" s="3"/>
       <c r="X47" s="3"/>
       <c r="Y47" s="3"/>
       <c r="Z47" s="3"/>
+      <c r="AA47" s="3"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>290</v>
+        <v>33</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="J48" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="K48" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L48" s="2" t="s">
-        <v>34</v>
+        <v>294</v>
+      </c>
+      <c r="I48" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="K48" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L48" s="2">
+        <v>5.0</v>
       </c>
       <c r="M48" s="2">
         <v>5.0</v>
       </c>
-      <c r="N48" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="O48" s="2" t="s">
-        <v>34</v>
+      <c r="N48" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O48" s="2">
+        <v>5.0</v>
       </c>
       <c r="P48" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="Q48" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="R48" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="S48" s="2"/>
-      <c r="T48" s="2" t="s">
-        <v>35</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="R48" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S48" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T48" s="2"/>
       <c r="U48" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V48" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="V48" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="W48" s="3"/>
       <c r="X48" s="3"/>
       <c r="Y48" s="3"/>
       <c r="Z48" s="3"/>
+      <c r="AA48" s="3"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="H49" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="J49" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="K49" s="2">
+        <v>33</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="I49" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M49" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N49" s="2">
         <v>2.0</v>
       </c>
-      <c r="L49" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M49" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="N49" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="O49" s="2">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="P49" s="2">
         <v>3.0</v>
       </c>
-      <c r="Q49" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R49" s="2">
-        <v>5.0</v>
+      <c r="Q49" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R49" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="S49" s="2" t="s">
-        <v>297</v>
+        <v>37</v>
       </c>
       <c r="T49" s="2" t="s">
-        <v>35</v>
+        <v>301</v>
       </c>
       <c r="U49" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V49" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="V49" s="2" t="s">
+        <v>148</v>
+      </c>
       <c r="W49" s="3"/>
       <c r="X49" s="3"/>
       <c r="Y49" s="3"/>
       <c r="Z49" s="3"/>
+      <c r="AA49" s="3"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="H50" s="2">
-        <v>9.0</v>
+        <v>33</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>305</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="J50" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="K50" s="2">
-        <v>5.0</v>
+        <v>35</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M50" s="2">
-        <v>5.0</v>
+        <v>37</v>
+      </c>
+      <c r="M50" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="O50" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="P50" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="Q50" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="R50" s="2">
-        <v>5.0</v>
+        <v>37</v>
+      </c>
+      <c r="O50" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P50" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q50" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R50" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="S50" s="2" t="s">
-        <v>303</v>
+        <v>37</v>
       </c>
       <c r="T50" s="2" t="s">
-        <v>35</v>
+        <v>307</v>
       </c>
       <c r="U50" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V50" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="V50" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="W50" s="3"/>
       <c r="X50" s="3"/>
       <c r="Y50" s="3"/>
       <c r="Z50" s="3"/>
+      <c r="AA50" s="3"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>307</v>
+        <v>33</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>50</v>
+        <v>311</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>308</v>
+        <v>35</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>34</v>
+        <v>312</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L51" s="2">
-        <v>5.0</v>
+        <v>37</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="P51" s="2">
-        <v>3.0</v>
+        <v>37</v>
+      </c>
+      <c r="P51" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="Q51" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="R51" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S51" s="2"/>
-      <c r="T51" s="2" t="s">
-        <v>45</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="R51" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S51" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T51" s="2"/>
       <c r="U51" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V51" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="V51" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="W51" s="3"/>
       <c r="X51" s="3"/>
       <c r="Y51" s="3"/>
       <c r="Z51" s="3"/>
+      <c r="AA51" s="3"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="H52" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="J52" s="2">
-        <v>5.0</v>
+        <v>33</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="I52" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>317</v>
       </c>
       <c r="K52" s="2">
         <v>5.0</v>
       </c>
       <c r="L52" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="M52" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="N52" s="2">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="O52" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="P52" s="2">
         <v>5.0</v>
@@ -4967,434 +5273,1031 @@
       <c r="R52" s="2">
         <v>5.0</v>
       </c>
-      <c r="S52" s="2" t="s">
-        <v>314</v>
+      <c r="S52" s="2">
+        <v>5.0</v>
       </c>
       <c r="T52" s="2" t="s">
-        <v>45</v>
+        <v>318</v>
       </c>
       <c r="U52" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V52" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="V52" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="W52" s="3"/>
       <c r="X52" s="3"/>
       <c r="Y52" s="3"/>
       <c r="Z52" s="3"/>
+      <c r="AA52" s="3"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>318</v>
+        <v>33</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
+      </c>
+      <c r="I53" s="2">
+        <v>8.0</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K53" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L53" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M53" s="2" t="s">
-        <v>34</v>
+        <v>323</v>
+      </c>
+      <c r="K53" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="L53" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M53" s="2">
+        <v>5.0</v>
       </c>
       <c r="N53" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O53" s="2" t="s">
-        <v>34</v>
+        <v>2.0</v>
+      </c>
+      <c r="O53" s="2">
+        <v>2.0</v>
       </c>
       <c r="P53" s="2">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="Q53" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="R53" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="S53" s="2" t="s">
-        <v>320</v>
+        <v>5.0</v>
+      </c>
+      <c r="R53" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="S53" s="2">
+        <v>5.0</v>
       </c>
       <c r="T53" s="2" t="s">
-        <v>45</v>
+        <v>324</v>
       </c>
       <c r="U53" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V53" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="V53" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="W53" s="3"/>
       <c r="X53" s="3"/>
       <c r="Y53" s="3"/>
       <c r="Z53" s="3"/>
+      <c r="AA53" s="3"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="H54" s="2">
-        <v>9.0</v>
+        <v>33</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>328</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>325</v>
+        <v>35</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>34</v>
+        <v>329</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q54" s="2">
-        <v>5.0</v>
+        <v>37</v>
+      </c>
+      <c r="Q54" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="R54" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="S54" s="2"/>
-      <c r="T54" s="2" t="s">
-        <v>45</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="S54" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T54" s="2"/>
       <c r="U54" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V54" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="V54" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="W54" s="3"/>
       <c r="X54" s="3"/>
       <c r="Y54" s="3"/>
       <c r="Z54" s="3"/>
+      <c r="AA54" s="3"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="H55" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="I55" s="2" t="s">
-        <v>330</v>
+        <v>68</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="I55" s="2">
+        <v>8.0</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>34</v>
+        <v>334</v>
       </c>
       <c r="K55" s="2">
         <v>5.0</v>
       </c>
       <c r="L55" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="M55" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N55" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="O55" s="2">
-        <v>5.0</v>
+        <v>5.0</v>
+      </c>
+      <c r="M55" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="N55" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O55" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q55" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R55" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="S55" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="T55" s="2" t="s">
-        <v>45</v>
-      </c>
+        <v>2.0</v>
+      </c>
+      <c r="R55" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="S55" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="T55" s="2"/>
       <c r="U55" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V55" s="3"/>
+        <v>72</v>
+      </c>
+      <c r="V55" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
+      <c r="AA55" s="3"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B56" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K56" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M56" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N56" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O56" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P56" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q56" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="R56" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C56" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="H56" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="I56" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="J56" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="K56" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L56" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="M56" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N56" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="O56" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="P56" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q56" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="R56" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S56" s="2"/>
-      <c r="T56" s="2" t="s">
-        <v>45</v>
-      </c>
+      <c r="S56" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T56" s="2"/>
       <c r="U56" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V56" s="3"/>
+        <v>72</v>
+      </c>
+      <c r="V56" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
+      <c r="AA56" s="3"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>340</v>
+        <v>68</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I57" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="J57" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="K57" s="2" t="s">
-        <v>34</v>
+        <v>343</v>
+      </c>
+      <c r="I57" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="K57" s="2">
+        <v>5.0</v>
       </c>
       <c r="L57" s="2">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="M57" s="2">
         <v>5.0</v>
       </c>
       <c r="N57" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P57" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="Q57" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R57" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="S57" s="2"/>
+        <v>3.0</v>
+      </c>
+      <c r="R57" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S57" s="2">
+        <v>5.0</v>
+      </c>
       <c r="T57" s="2" t="s">
-        <v>45</v>
+        <v>345</v>
       </c>
       <c r="U57" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V57" s="3"/>
+        <v>72</v>
+      </c>
+      <c r="V57" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="W57" s="3"/>
       <c r="X57" s="3"/>
       <c r="Y57" s="3"/>
       <c r="Z57" s="3"/>
+      <c r="AA57" s="3"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>345</v>
+        <v>68</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I58" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="J58" s="2">
-        <v>5.0</v>
+        <v>349</v>
+      </c>
+      <c r="I58" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>350</v>
       </c>
       <c r="K58" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="L58" s="2">
         <v>5.0</v>
       </c>
-      <c r="M58" s="2">
-        <v>5.0</v>
+      <c r="M58" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="N58" s="2">
         <v>5.0</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="P58" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="P58" s="2">
+        <v>4.0</v>
       </c>
       <c r="Q58" s="2">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="R58" s="2">
         <v>4.0</v>
       </c>
-      <c r="S58" s="2" t="s">
-        <v>347</v>
+      <c r="S58" s="2">
+        <v>5.0</v>
       </c>
       <c r="T58" s="2" t="s">
-        <v>45</v>
+        <v>351</v>
       </c>
       <c r="U58" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V58" s="3"/>
+        <v>72</v>
+      </c>
+      <c r="V58" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="W58" s="3"/>
       <c r="X58" s="3"/>
       <c r="Y58" s="3"/>
       <c r="Z58" s="3"/>
+      <c r="AA58" s="3"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L59" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M59" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N59" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O59" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P59" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q59" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="R59" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S59" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T59" s="2"/>
+      <c r="U59" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="V59" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="W59" s="3"/>
+      <c r="X59" s="3"/>
+      <c r="Y59" s="3"/>
+      <c r="Z59" s="3"/>
+      <c r="AA59" s="3"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="I60" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="K60" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L60" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M60" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N60" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O60" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P60" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q60" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R60" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S60" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T60" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="U60" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="V60" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="W60" s="3"/>
+      <c r="X60" s="3"/>
+      <c r="Y60" s="3"/>
+      <c r="Z60" s="3"/>
+      <c r="AA60" s="3"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L61" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M61" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N61" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O61" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P61" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q61" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="R61" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="S61" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T61" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="U61" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="V61" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="W61" s="3"/>
+      <c r="X61" s="3"/>
+      <c r="Y61" s="3"/>
+      <c r="Z61" s="3"/>
+      <c r="AA61" s="3"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="I62" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L62" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M62" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N62" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O62" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P62" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q62" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R62" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S62" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T62" s="3"/>
+      <c r="U62" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="V62" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="W62" s="3"/>
+      <c r="X62" s="3"/>
+      <c r="Y62" s="3"/>
+      <c r="Z62" s="3"/>
+      <c r="AA62" s="3"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="I63" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L63" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M63" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="N63" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O63" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="P63" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q63" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R63" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S63" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T63" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="U63" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="V63" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="W63" s="3"/>
+      <c r="X63" s="3"/>
+      <c r="Y63" s="3"/>
+      <c r="Z63" s="3"/>
+      <c r="AA63" s="3"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="I64" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="K64" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M64" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="N64" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O64" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P64" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q64" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R64" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S64" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T64" s="3"/>
+      <c r="U64" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="V64" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="W64" s="3"/>
+      <c r="X64" s="3"/>
+      <c r="Y64" s="3"/>
+      <c r="Z64" s="3"/>
+      <c r="AA64" s="3"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="K65" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L65" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M65" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N65" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O65" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P65" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q65" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R65" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S65" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T65" s="3"/>
+      <c r="U65" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="V65" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="W65" s="3"/>
+      <c r="X65" s="3"/>
+      <c r="Y65" s="3"/>
+      <c r="Z65" s="3"/>
+      <c r="AA65" s="3"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="K66" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L66" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M66" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N66" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O66" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P66" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q66" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R66" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="S66" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="T66" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="U66" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="V66" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="W66" s="3"/>
+      <c r="X66" s="3"/>
+      <c r="Y66" s="3"/>
+      <c r="Z66" s="3"/>
+      <c r="AA66" s="3"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/NPS - matriz-novaiguacu.xlsx
+++ b/NPS - matriz-novaiguacu.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="442">
   <si>
     <t>userId</t>
   </si>
@@ -73,9 +73,6 @@
     <t>Estamos interessados ​​em ouvir suas ideias! Por favor, compartilhe suas sugestões ou comentários</t>
   </si>
   <si>
-    <t>Tipo Respondente</t>
-  </si>
-  <si>
     <t>Perfil</t>
   </si>
   <si>
@@ -91,49 +88,210 @@
     <t>AÇÃO</t>
   </si>
   <si>
-    <t>Última atualização: 25/03/2026 18:31</t>
+    <t>Última atualização: 30/03/2026 14:47</t>
+  </si>
+  <si>
+    <t>Última atualização: 26/03/2026 14:31</t>
+  </si>
+  <si>
+    <t>65bd13ef47903202e81613ad</t>
+  </si>
+  <si>
+    <t>69b898af21c08e4e2e112204</t>
+  </si>
+  <si>
+    <t>Queremos ouvir a sua opinião</t>
+  </si>
+  <si>
+    <t>matriz-novaiguacu</t>
+  </si>
+  <si>
+    <t>GIOVANNA SALAZAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>giovannamt24138703@matrizeducacao.com.br</t>
+  </si>
+  <si>
+    <t>estudante</t>
+  </si>
+  <si>
+    <t>2026-03-28T22:49:50.713Z</t>
+  </si>
+  <si>
+    <t>0 - Nada provável</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pois poderiam melhorar o banheiro que não é arrumado a anos, nao tem uma porra que feche direto!!! mudar a forma de escutar alguns pontos dos alunos e nn passar a mao na cabeça de comportamento que não são admissíveis para qualquer pessoa que vive na sociedade atual!!! melhorar tbm o valor da cantina , colocar uma cantina com preço ms acessível para todos! colocar uma tolerância maior para entrada dentro de sala. administrar melhor o planejamento de aula… entre outras mil reclamações do matriz educação </t>
+  </si>
+  <si>
+    <t>6 - Muito Satisfeito</t>
+  </si>
+  <si>
+    <t>1 - Muito Insatisfeito</t>
+  </si>
+  <si>
+    <t>melhore tudo, pq ta pessimo, e estão perdendo aluno por isso</t>
+  </si>
+  <si>
+    <t>Detrator</t>
+  </si>
+  <si>
+    <t>693222776b0fec5e3b5c2525</t>
+  </si>
+  <si>
+    <t>GUTHIERRY DE MIRANDA MACHADO RIBEIRO</t>
+  </si>
+  <si>
+    <t>guthierrymt25186792@matrizeducacao.com.br</t>
+  </si>
+  <si>
+    <t>2026-03-28T05:03:45.017Z</t>
+  </si>
+  <si>
+    <t>Uma escola totalmente diferenciada, entrega muito pelo preço e realmente dá a oportunidade para os alunos participarem das decisões sobre eles mesmos, a escola escuta e apoia os alunos, fora eventos e algumas atividades extras opcionais, algo que também diferencia bastante a escola de boa forma.</t>
+  </si>
+  <si>
+    <t>Eu sendo um aluno, já conversei com diversos amigos sobre a cantina e seus preços, e como conclusão dessas conversas, percebo que todos reclamam do preço da cantina, mas por ser "o único" modo de comprar algo para comer no recreio, muitos compram mesmo não gostando do preço. Uma sugestão, se for possível, abaixar em R$1-2 já está de bom grado para todos, dependendo do salgado e da bebida.</t>
+  </si>
+  <si>
+    <t>Promotor</t>
+  </si>
+  <si>
+    <t>698b56f7651157b85e01f2e3</t>
+  </si>
+  <si>
+    <t>69b86aba3648364cda618874</t>
+  </si>
+  <si>
+    <t>ALANA DE CASTRO LOPES</t>
+  </si>
+  <si>
+    <t>alanalopesseoud@gmail.com</t>
+  </si>
+  <si>
+    <t>responsavel</t>
+  </si>
+  <si>
+    <t>2026-03-27T13:42:42.278Z</t>
+  </si>
+  <si>
+    <t>10 - Extremamente provável</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escola excelente </t>
+  </si>
+  <si>
+    <t>Estou satisfeita com a escola.</t>
+  </si>
+  <si>
+    <t>677bc2375316899ca2c5b77c</t>
+  </si>
+  <si>
+    <t>MICHELE DA SILVA SANTOS</t>
+  </si>
+  <si>
+    <t>micheledasilvasantos78@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-26T21:50:26.633Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ainda estou conhecendo o sistema da escola. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poderia vender comida ou ter alguma empresa que forneça quentinha para quem fica no contraturno. </t>
+  </si>
+  <si>
+    <t>66be18ddd89025d6c6b2344c</t>
+  </si>
+  <si>
+    <t>LUIZ FERNANDO RODRIGUES DOS SANTOS</t>
+  </si>
+  <si>
+    <t>luizmt24146714@matrizeducacao.com.br</t>
+  </si>
+  <si>
+    <t>2026-03-26T19:02:26.891Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.
+</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>677bc238531689a3f4c5b8ae</t>
+  </si>
+  <si>
+    <t>JULIANA DUARTE DE CARVALHO NUNES</t>
+  </si>
+  <si>
+    <t>julianaduarte.vendas@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-26T11:06:15.618Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eu gosto da escola e não tenho o que reclamar. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A reunião com os diretores do ano passado eu achei de extrema importância, acho que deve acontecer pelo menos uma vez ao ano. </t>
+  </si>
+  <si>
+    <t>698b56f7651157d27c01f2de</t>
+  </si>
+  <si>
+    <t>ADRIELY DUANY CARDOSO GONÇALVES</t>
+  </si>
+  <si>
+    <t>adriely.duany@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-25T23:25:51.699Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Até o momento estou gostando </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precisa melhorar o pátio em Nova Iguaçu 
+Aulas de inglês precisa de mais didática
+</t>
+  </si>
+  <si>
+    <t>677bc23853168965dac5b8bf</t>
+  </si>
+  <si>
+    <t>MONICA CRISTIANE COELHO PERARO</t>
+  </si>
+  <si>
+    <t>mcoelhoperaro@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-25T22:15:18.519Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualidade de ensino, seriedade, estímulo ao aprendizado </t>
+  </si>
+  <si>
+    <t>Os alunos carregam mt peso devido aos materiais de estudos. E tem mta morosidade para liberação do armário.
+Ano passado por exemplo só foi liberado quase no final do ano.
+Então essa morosidade prejudica mt, pois tem alunos que moram longe e dependem de transporte público, enfrentam engarrafamento e andam bastante do ponto do seu ônibus até chegar na escola e ao sair.</t>
   </si>
   <si>
     <t>62261c5768ca0d001c229386</t>
   </si>
   <si>
-    <t>69b86aba3648364cda618874</t>
-  </si>
-  <si>
-    <t>Queremos ouvir a sua opinião</t>
-  </si>
-  <si>
-    <t>matriz-novaiguacu</t>
-  </si>
-  <si>
     <t>MARQUIASIO PAULIQUEVIS</t>
   </si>
   <si>
     <t>pauliquevismarquiasio@gmail.com</t>
   </si>
   <si>
-    <t>responsavel</t>
-  </si>
-  <si>
     <t>2026-03-25T20:30:30.073Z</t>
   </si>
   <si>
-    <t>10 - Extremamente provável</t>
-  </si>
-  <si>
     <t xml:space="preserve">Eu acho que o ensino é maravilhoso </t>
-  </si>
-  <si>
-    <t>6 - Muito Satisfeito</t>
-  </si>
-  <si>
-    <t>1 - Muito Insatisfeito</t>
-  </si>
-  <si>
-    <t>Responsável</t>
-  </si>
-  <si>
-    <t>Promotor</t>
   </si>
   <si>
     <t>6785ab10f184ec03d2c8a748</t>
@@ -213,18 +371,12 @@
     <t>633e0945a58df4001d6a7359</t>
   </si>
   <si>
-    <t>69b898af21c08e4e2e112204</t>
-  </si>
-  <si>
     <t>LUAN RAPHAEL DA ROCHA TAVARES</t>
   </si>
   <si>
     <t>luanmt22088918@matrizeducacao.com.br</t>
   </si>
   <si>
-    <t>estudante</t>
-  </si>
-  <si>
     <t>2026-03-24T20:58:30.857Z</t>
   </si>
   <si>
@@ -232,9 +384,6 @@
   </si>
   <si>
     <t>abaixem os preços na cantina, está tudo um absurdo que é incomparável aos preços dos mesmos produtos fora da escola</t>
-  </si>
-  <si>
-    <t>Aluno</t>
   </si>
   <si>
     <t>69658cd4c2a9c98a06e28079</t>
@@ -387,9 +536,6 @@
     <t>ainda estou me adaptando aqui nesta escola</t>
   </si>
   <si>
-    <t>.</t>
-  </si>
-  <si>
     <t>697bbf8f2dd633786f4a0f6a</t>
   </si>
   <si>
@@ -464,9 +610,6 @@
   </si>
   <si>
     <t xml:space="preserve">Maior demora pra sair o gabarito do </t>
-  </si>
-  <si>
-    <t>Detrator</t>
   </si>
   <si>
     <t>677bc237531689faa7c5b5f8</t>
@@ -1515,7 +1658,7 @@
     <col customWidth="1" min="7" max="7" width="13.38"/>
     <col customWidth="1" min="8" max="8" width="20.5"/>
     <col customWidth="1" min="9" max="9" width="68.0"/>
-    <col customWidth="1" min="10" max="10" width="309.63"/>
+    <col customWidth="1" min="10" max="10" width="380.25"/>
     <col customWidth="1" min="11" max="11" width="67.63"/>
     <col customWidth="1" min="12" max="12" width="71.63"/>
     <col customWidth="1" min="13" max="13" width="74.13"/>
@@ -1526,13 +1669,12 @@
     <col customWidth="1" min="18" max="18" width="69.38"/>
     <col customWidth="1" min="19" max="19" width="62.0"/>
     <col customWidth="1" min="20" max="20" width="831.5"/>
-    <col customWidth="1" min="21" max="21" width="14.25"/>
-    <col customWidth="1" min="22" max="22" width="7.75"/>
-    <col customWidth="1" min="23" max="23" width="12.75"/>
-    <col customWidth="1" min="24" max="24" width="24.13"/>
-    <col customWidth="1" min="25" max="25" width="16.38"/>
-    <col customWidth="1" min="26" max="26" width="5.25"/>
-    <col customWidth="1" min="27" max="27" width="28.63"/>
+    <col customWidth="1" min="21" max="21" width="7.75"/>
+    <col customWidth="1" min="22" max="22" width="12.75"/>
+    <col customWidth="1" min="23" max="23" width="24.13"/>
+    <col customWidth="1" min="24" max="24" width="16.38"/>
+    <col customWidth="1" min="25" max="25" width="5.25"/>
+    <col customWidth="1" min="26" max="27" width="28.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1652,37 +1794,37 @@
       <c r="K2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>37</v>
+      <c r="L2" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="M2" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N2" s="2">
+        <v>2.0</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="2" t="s">
-        <v>37</v>
+      <c r="P2" s="2">
+        <v>2.0</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="S2" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="T2" s="2"/>
+      <c r="S2" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="U2" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V2" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="V2" s="2"/>
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
@@ -1715,47 +1857,45 @@
         <v>44</v>
       </c>
       <c r="I3" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>45</v>
       </c>
       <c r="K3" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O3" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="P3" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R3" s="2">
         <v>3.0</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M3" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="N3" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O3" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P3" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="Q3" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R3" s="2">
-        <v>4.0</v>
-      </c>
       <c r="S3" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="T3" s="2" t="s">
         <v>46</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V3" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="V3" s="2"/>
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
       <c r="Y3" s="3"/>
@@ -1767,7 +1907,7 @@
         <v>48</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>29</v>
@@ -1776,59 +1916,57 @@
         <v>30</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I4" s="2">
-        <v>8.0</v>
+        <v>53</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="K4" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L4" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="M4" s="2">
-        <v>5.0</v>
+        <v>55</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="N4" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="O4" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P4" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="Q4" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="R4" s="2">
         <v>5.0</v>
       </c>
-      <c r="S4" s="2" t="s">
-        <v>37</v>
+      <c r="S4" s="2">
+        <v>5.0</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V4" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="V4" s="2"/>
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
@@ -1837,10 +1975,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>29</v>
@@ -1849,57 +1987,57 @@
         <v>30</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>35</v>
+        <v>60</v>
+      </c>
+      <c r="I5" s="2">
+        <v>9.0</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>37</v>
+        <v>61</v>
+      </c>
+      <c r="K5" s="2">
+        <v>5.0</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="M5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>37</v>
+      <c r="M5" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N5" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O5" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P5" s="2">
+        <v>5.0</v>
       </c>
       <c r="Q5" s="2" t="s">
         <v>37</v>
       </c>
       <c r="R5" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="S5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="T5" s="2"/>
+      <c r="T5" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="U5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V5" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V5" s="2"/>
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
       <c r="Y5" s="3"/>
@@ -1908,7 +2046,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>28</v>
@@ -1920,40 +2058,40 @@
         <v>30</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I6" s="2">
-        <v>9.0</v>
+        <v>66</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="K6" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L6" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M6" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N6" s="2">
-        <v>5.0</v>
+        <v>67</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="P6" s="2">
-        <v>5.0</v>
+      <c r="P6" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>37</v>
@@ -1964,13 +2102,13 @@
       <c r="S6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="T6" s="2"/>
+      <c r="T6" s="2" t="s">
+        <v>68</v>
+      </c>
       <c r="U6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V6" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V6" s="2"/>
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
@@ -1979,10 +2117,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>29</v>
@@ -1991,59 +2129,57 @@
         <v>30</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="I7" s="2">
-        <v>7.0</v>
+        <v>72</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="L7" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="M7" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="N7" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O7" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P7" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q7" s="2">
-        <v>3.0</v>
+      <c r="L7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="S7" s="2">
-        <v>4.0</v>
+        <v>37</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="V7" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="V7" s="2"/>
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
       <c r="Y7" s="3"/>
@@ -2052,10 +2188,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>29</v>
@@ -2064,28 +2200,28 @@
         <v>30</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I8" s="2">
         <v>9.0</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>37</v>
+        <v>79</v>
+      </c>
+      <c r="K8" s="2">
+        <v>5.0</v>
       </c>
       <c r="L8" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="M8" s="2">
         <v>5.0</v>
@@ -2093,30 +2229,28 @@
       <c r="N8" s="2">
         <v>5.0</v>
       </c>
-      <c r="O8" s="2" t="s">
-        <v>37</v>
+      <c r="O8" s="2">
+        <v>5.0</v>
       </c>
       <c r="P8" s="2">
         <v>5.0</v>
       </c>
-      <c r="Q8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="S8" s="2" t="s">
-        <v>37</v>
+      <c r="Q8" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R8" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="S8" s="2">
+        <v>4.0</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V8" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V8" s="2"/>
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
@@ -2125,10 +2259,10 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -2137,59 +2271,57 @@
         <v>30</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L9" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>37</v>
+        <v>85</v>
+      </c>
+      <c r="K9" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M9" s="2">
+        <v>5.0</v>
       </c>
       <c r="N9" s="2">
         <v>5.0</v>
       </c>
-      <c r="O9" s="2">
-        <v>5.0</v>
+      <c r="O9" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="Q9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>37</v>
+      <c r="Q9" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R9" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S9" s="2">
+        <v>5.0</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V9" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V9" s="2"/>
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
@@ -2198,10 +2330,10 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>29</v>
@@ -2210,28 +2342,28 @@
         <v>30</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="I10" s="2">
-        <v>7.0</v>
+        <v>90</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="L10" s="2">
-        <v>5.0</v>
+      <c r="L10" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="M10" s="2" t="s">
         <v>37</v>
@@ -2248,19 +2380,17 @@
       <c r="Q10" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="R10" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S10" s="2">
-        <v>5.0</v>
+      <c r="R10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="T10" s="2"/>
       <c r="U10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="V10" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="V10" s="2"/>
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
@@ -2269,10 +2399,10 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>29</v>
@@ -2281,34 +2411,34 @@
         <v>30</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I11" s="2">
         <v>7.0</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K11" s="2">
         <v>3.0</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M11" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>37</v>
+        <v>3.0</v>
+      </c>
+      <c r="N11" s="2">
+        <v>5.0</v>
       </c>
       <c r="O11" s="2">
         <v>5.0</v>
@@ -2316,8 +2446,8 @@
       <c r="P11" s="2">
         <v>4.0</v>
       </c>
-      <c r="Q11" s="2" t="s">
-        <v>38</v>
+      <c r="Q11" s="2">
+        <v>5.0</v>
       </c>
       <c r="R11" s="2">
         <v>4.0</v>
@@ -2326,14 +2456,12 @@
         <v>5.0</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V11" s="2" t="s">
-        <v>47</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="V11" s="2"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
@@ -2342,10 +2470,10 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>29</v>
@@ -2354,57 +2482,57 @@
         <v>30</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F12" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I12" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="K12" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L12" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="M12" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N12" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="O12" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="P12" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="R12" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="U12" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O12" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="S12" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="T12" s="2"/>
-      <c r="U12" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V12" s="2" t="s">
-        <v>40</v>
-      </c>
+      <c r="V12" s="2"/>
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
@@ -2413,10 +2541,10 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>29</v>
@@ -2425,57 +2553,55 @@
         <v>30</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="K13" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L13" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M13" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N13" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O13" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P13" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q13" s="2">
-        <v>4.0</v>
+        <v>109</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="R13" s="2">
         <v>4.0</v>
       </c>
-      <c r="S13" s="2">
-        <v>5.0</v>
+      <c r="S13" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="T13" s="2"/>
       <c r="U13" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V13" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V13" s="2"/>
       <c r="W13" s="3"/>
       <c r="X13" s="3"/>
       <c r="Y13" s="3"/>
@@ -2484,10 +2610,10 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>29</v>
@@ -2496,22 +2622,22 @@
         <v>30</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>35</v>
+        <v>113</v>
+      </c>
+      <c r="I14" s="2">
+        <v>9.0</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="K14" s="2">
         <v>5.0</v>
@@ -2523,30 +2649,28 @@
         <v>5.0</v>
       </c>
       <c r="N14" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="O14" s="2">
-        <v>5.0</v>
+        <v>5.0</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P14" s="2">
         <v>5.0</v>
       </c>
-      <c r="Q14" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R14" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S14" s="2">
-        <v>5.0</v>
+      <c r="Q14" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="T14" s="2"/>
       <c r="U14" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V14" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V14" s="2"/>
       <c r="W14" s="3"/>
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
@@ -2555,7 +2679,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>28</v>
@@ -2567,31 +2691,31 @@
         <v>30</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="I15" s="2">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="K15" s="2">
-        <v>5.0</v>
+        <v>119</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="L15" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="M15" s="2">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="N15" s="2">
         <v>5.0</v>
@@ -2602,24 +2726,22 @@
       <c r="P15" s="2">
         <v>5.0</v>
       </c>
-      <c r="Q15" s="2" t="s">
+      <c r="Q15" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="R15" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="R15" s="2">
-        <v>5.0</v>
-      </c>
       <c r="S15" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V15" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="V15" s="2"/>
       <c r="W15" s="3"/>
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
@@ -2628,10 +2750,10 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
@@ -2640,59 +2762,57 @@
         <v>30</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="I16" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="L16" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>37</v>
+      <c r="L16" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M16" s="2">
+        <v>5.0</v>
       </c>
       <c r="N16" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>37</v>
       </c>
       <c r="P16" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="Q16" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="R16" s="2">
-        <v>5.0</v>
+        <v>5.0</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="S16" s="2" t="s">
         <v>37</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="V16" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="V16" s="2"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
@@ -2701,10 +2821,10 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>29</v>
@@ -2713,31 +2833,31 @@
         <v>30</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I17" s="2">
-        <v>8.0</v>
+        <v>130</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="K17" s="2">
-        <v>5.0</v>
+        <v>131</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="L17" s="2">
         <v>5.0</v>
       </c>
-      <c r="M17" s="2">
-        <v>4.0</v>
+      <c r="M17" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="N17" s="2">
         <v>5.0</v>
@@ -2745,27 +2865,25 @@
       <c r="O17" s="2">
         <v>5.0</v>
       </c>
-      <c r="P17" s="2">
-        <v>5.0</v>
+      <c r="P17" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="Q17" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="R17" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="S17" s="2">
-        <v>5.0</v>
+      <c r="R17" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="U17" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V17" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="V17" s="2"/>
       <c r="W17" s="3"/>
       <c r="X17" s="3"/>
       <c r="Y17" s="3"/>
@@ -2774,7 +2892,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>28</v>
@@ -2786,28 +2904,28 @@
         <v>30</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>35</v>
+        <v>136</v>
+      </c>
+      <c r="I18" s="2">
+        <v>7.0</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="L18" s="2" t="s">
-        <v>37</v>
+      <c r="L18" s="2">
+        <v>5.0</v>
       </c>
       <c r="M18" s="2" t="s">
         <v>37</v>
@@ -2821,22 +2939,20 @@
       <c r="P18" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="Q18" s="2">
-        <v>4.0</v>
+      <c r="Q18" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="R18" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="S18" s="2" t="s">
-        <v>37</v>
+        <v>5.0</v>
+      </c>
+      <c r="S18" s="2">
+        <v>5.0</v>
       </c>
       <c r="T18" s="2"/>
       <c r="U18" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V18" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="V18" s="2"/>
       <c r="W18" s="3"/>
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
@@ -2845,10 +2961,10 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>29</v>
@@ -2857,57 +2973,57 @@
         <v>30</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="I19" s="2">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>37</v>
+        <v>142</v>
+      </c>
+      <c r="K19" s="2">
+        <v>3.0</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="M19" s="2">
+        <v>4.0</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="O19" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>37</v>
+      <c r="O19" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P19" s="2">
+        <v>4.0</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="R19" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="S19" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="T19" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="R19" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="S19" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T19" s="2" t="s">
+        <v>143</v>
+      </c>
       <c r="U19" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V19" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="V19" s="2"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
@@ -2916,10 +3032,10 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>29</v>
@@ -2928,22 +3044,22 @@
         <v>30</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>37</v>
@@ -2957,8 +3073,8 @@
       <c r="N20" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="O20" s="2" t="s">
-        <v>37</v>
+      <c r="O20" s="2">
+        <v>4.0</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>37</v>
@@ -2974,11 +3090,9 @@
       </c>
       <c r="T20" s="2"/>
       <c r="U20" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V20" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V20" s="2"/>
       <c r="W20" s="3"/>
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
@@ -2987,10 +3101,10 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>29</v>
@@ -2999,59 +3113,55 @@
         <v>30</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I21" s="2">
-        <v>5.0</v>
+        <v>152</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="K21" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="L21" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="M21" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="N21" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="O21" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="P21" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="Q21" s="2">
         <v>4.0</v>
       </c>
       <c r="R21" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="S21" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="T21" s="2" t="s">
-        <v>147</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="T21" s="2"/>
       <c r="U21" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="V21" s="2" t="s">
-        <v>148</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V21" s="2"/>
       <c r="W21" s="3"/>
       <c r="X21" s="3"/>
       <c r="Y21" s="3"/>
@@ -3060,10 +3170,10 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>29</v>
@@ -3072,40 +3182,40 @@
         <v>30</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O22" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="P22" s="2" t="s">
-        <v>37</v>
+        <v>158</v>
+      </c>
+      <c r="K22" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L22" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M22" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N22" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="O22" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P22" s="2">
+        <v>5.0</v>
       </c>
       <c r="Q22" s="2">
         <v>5.0</v>
@@ -3113,16 +3223,14 @@
       <c r="R22" s="2">
         <v>5.0</v>
       </c>
-      <c r="S22" s="2" t="s">
-        <v>37</v>
+      <c r="S22" s="2">
+        <v>5.0</v>
       </c>
       <c r="T22" s="2"/>
       <c r="U22" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V22" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V22" s="2"/>
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
       <c r="Y22" s="3"/>
@@ -3131,10 +3239,10 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>29</v>
@@ -3143,57 +3251,57 @@
         <v>30</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>35</v>
+        <v>162</v>
+      </c>
+      <c r="I23" s="2">
+        <v>9.0</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O23" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="P23" s="2" t="s">
-        <v>37</v>
+        <v>163</v>
+      </c>
+      <c r="K23" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L23" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M23" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N23" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O23" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P23" s="2">
+        <v>5.0</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="R23" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="S23" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="T23" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="R23" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S23" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T23" s="2" t="s">
+        <v>164</v>
+      </c>
       <c r="U23" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V23" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V23" s="2"/>
       <c r="W23" s="3"/>
       <c r="X23" s="3"/>
       <c r="Y23" s="3"/>
@@ -3202,7 +3310,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>28</v>
@@ -3214,22 +3322,22 @@
         <v>30</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>35</v>
+        <v>168</v>
+      </c>
+      <c r="I24" s="2">
+        <v>8.0</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>37</v>
@@ -3240,31 +3348,31 @@
       <c r="M24" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="N24" s="2" t="s">
-        <v>37</v>
+      <c r="N24" s="2">
+        <v>4.0</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="P24" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q24" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="R24" s="2" t="s">
-        <v>37</v>
+      <c r="P24" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="Q24" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="R24" s="2">
+        <v>5.0</v>
       </c>
       <c r="S24" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="T24" s="2"/>
+      <c r="T24" s="2" t="s">
+        <v>68</v>
+      </c>
       <c r="U24" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V24" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="V24" s="2"/>
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
@@ -3273,10 +3381,10 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>29</v>
@@ -3285,59 +3393,57 @@
         <v>30</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="G25" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="I25" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="J25" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="H25" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="I25" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>37</v>
+      <c r="K25" s="2">
+        <v>5.0</v>
       </c>
       <c r="L25" s="2">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="M25" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="N25" s="2">
         <v>5.0</v>
       </c>
       <c r="O25" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="P25" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R25" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="S25" s="2">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>169</v>
+        <v>68</v>
       </c>
       <c r="U25" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="V25" s="2" t="s">
-        <v>148</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="V25" s="2"/>
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
       <c r="Y25" s="3"/>
@@ -3346,10 +3452,10 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>29</v>
@@ -3358,31 +3464,31 @@
         <v>30</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="I26" s="2">
-        <v>8.0</v>
+        <v>177</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="K26" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L26" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M26" s="2">
-        <v>5.0</v>
+        <v>178</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>37</v>
@@ -3390,25 +3496,23 @@
       <c r="O26" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="P26" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q26" s="2" t="s">
-        <v>37</v>
+      <c r="P26" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q26" s="2">
+        <v>4.0</v>
       </c>
       <c r="R26" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="S26" s="2" t="s">
         <v>37</v>
       </c>
       <c r="T26" s="2"/>
       <c r="U26" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V26" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="V26" s="2"/>
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
       <c r="Y26" s="3"/>
@@ -3417,10 +3521,10 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>29</v>
@@ -3429,22 +3533,22 @@
         <v>30</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>35</v>
+        <v>182</v>
+      </c>
+      <c r="I27" s="2">
+        <v>9.0</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>37</v>
@@ -3470,18 +3574,14 @@
       <c r="R27" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="S27" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="T27" s="2" t="s">
-        <v>180</v>
-      </c>
+      <c r="S27" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T27" s="2"/>
       <c r="U27" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V27" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V27" s="2"/>
       <c r="W27" s="3"/>
       <c r="X27" s="3"/>
       <c r="Y27" s="3"/>
@@ -3490,10 +3590,10 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>29</v>
@@ -3502,59 +3602,55 @@
         <v>30</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="I28" s="2">
-        <v>8.0</v>
+        <v>187</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="K28" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L28" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M28" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N28" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O28" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P28" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q28" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R28" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S28" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="T28" s="2" t="s">
-        <v>186</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q28" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R28" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S28" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T28" s="2"/>
       <c r="U28" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="V28" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="V28" s="2"/>
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
@@ -3563,10 +3659,10 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>29</v>
@@ -3575,59 +3671,57 @@
         <v>30</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I29" s="2">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L29" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M29" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="N29" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O29" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="P29" s="2" t="s">
-        <v>37</v>
+        <v>193</v>
+      </c>
+      <c r="K29" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="L29" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="M29" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N29" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="O29" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="P29" s="2">
+        <v>3.0</v>
       </c>
       <c r="Q29" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="R29" s="2">
         <v>3.0</v>
       </c>
-      <c r="R29" s="2">
-        <v>5.0</v>
-      </c>
       <c r="S29" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="T29" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="U29" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="V29" s="2" t="s">
-        <v>47</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="V29" s="2"/>
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
       <c r="Y29" s="3"/>
@@ -3636,10 +3730,10 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>29</v>
@@ -3648,59 +3742,55 @@
         <v>30</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="I30" s="2">
-        <v>7.0</v>
+        <v>198</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="K30" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L30" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M30" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N30" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O30" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P30" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q30" s="2" t="s">
-        <v>38</v>
+        <v>199</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q30" s="2">
+        <v>5.0</v>
       </c>
       <c r="R30" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="S30" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="T30" s="2" t="s">
-        <v>198</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="S30" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T30" s="2"/>
       <c r="U30" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V30" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="V30" s="2"/>
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
       <c r="Y30" s="3"/>
@@ -3709,10 +3799,10 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>29</v>
@@ -3721,59 +3811,55 @@
         <v>30</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="I31" s="2">
-        <v>6.0</v>
+        <v>203</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="K31" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="L31" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="M31" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="N31" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="O31" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="P31" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="Q31" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="R31" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="S31" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="T31" s="2" t="s">
         <v>204</v>
       </c>
+      <c r="K31" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q31" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R31" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S31" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T31" s="2"/>
       <c r="U31" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V31" s="2" t="s">
-        <v>148</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V31" s="2"/>
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
       <c r="Y31" s="3"/>
@@ -3785,7 +3871,7 @@
         <v>205</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>29</v>
@@ -3800,13 +3886,13 @@
         <v>207</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="I32" s="2">
-        <v>8.0</v>
+      <c r="I32" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>209</v>
@@ -3814,37 +3900,35 @@
       <c r="K32" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="L32" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="M32" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="N32" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="O32" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="P32" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="Q32" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="R32" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="S32" s="2">
-        <v>5.0</v>
+      <c r="L32" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N32" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O32" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P32" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q32" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R32" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S32" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="T32" s="2"/>
       <c r="U32" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V32" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="V32" s="2"/>
       <c r="W32" s="3"/>
       <c r="X32" s="3"/>
       <c r="Y32" s="3"/>
@@ -3877,47 +3961,45 @@
         <v>213</v>
       </c>
       <c r="I33" s="2">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="K33" s="2">
-        <v>5.0</v>
+        <v>214</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="L33" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="M33" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="N33" s="2" t="s">
+        <v>2.0</v>
+      </c>
+      <c r="M33" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N33" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O33" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="P33" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="Q33" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="O33" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="P33" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="Q33" s="2">
-        <v>4.0</v>
-      </c>
       <c r="R33" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="S33" s="2" t="s">
-        <v>37</v>
+        <v>5.0</v>
+      </c>
+      <c r="S33" s="2">
+        <v>2.0</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="U33" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V33" s="2" t="s">
-        <v>47</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="V33" s="2"/>
       <c r="W33" s="3"/>
       <c r="X33" s="3"/>
       <c r="Y33" s="3"/>
@@ -3926,10 +4008,10 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>29</v>
@@ -3938,57 +4020,55 @@
         <v>30</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I34" s="2">
         <v>8.0</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K34" s="2">
         <v>5.0</v>
       </c>
       <c r="L34" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="M34" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="N34" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O34" s="2">
-        <v>5.0</v>
+        <v>5.0</v>
+      </c>
+      <c r="M34" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N34" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O34" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P34" s="2">
         <v>5.0</v>
       </c>
-      <c r="Q34" s="2">
-        <v>5.0</v>
+      <c r="Q34" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="R34" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="S34" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
+      </c>
+      <c r="S34" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="T34" s="2"/>
       <c r="U34" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V34" s="2" t="s">
-        <v>47</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="V34" s="2"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
@@ -3997,10 +4077,10 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>29</v>
@@ -4009,57 +4089,57 @@
         <v>30</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="I35" s="2">
-        <v>9.0</v>
+        <v>224</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="K35" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L35" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M35" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N35" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O35" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P35" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q35" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R35" s="2">
-        <v>5.0</v>
+        <v>225</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R35" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="S35" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="T35" s="2"/>
+        <v>3.0</v>
+      </c>
+      <c r="T35" s="2" t="s">
+        <v>226</v>
+      </c>
       <c r="U35" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V35" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V35" s="2"/>
       <c r="W35" s="3"/>
       <c r="X35" s="3"/>
       <c r="Y35" s="3"/>
@@ -4068,7 +4148,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>28</v>
@@ -4080,59 +4160,57 @@
         <v>30</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>35</v>
+        <v>230</v>
+      </c>
+      <c r="I36" s="2">
+        <v>8.0</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M36" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="N36" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O36" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="P36" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q36" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="R36" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="S36" s="2" t="s">
-        <v>37</v>
+        <v>231</v>
+      </c>
+      <c r="K36" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L36" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M36" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N36" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O36" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P36" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q36" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R36" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S36" s="2">
+        <v>5.0</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="U36" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V36" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="V36" s="2"/>
       <c r="W36" s="3"/>
       <c r="X36" s="3"/>
       <c r="Y36" s="3"/>
@@ -4141,7 +4219,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>28</v>
@@ -4153,43 +4231,43 @@
         <v>30</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I37" s="2">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="K37" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L37" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M37" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N37" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O37" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P37" s="2">
-        <v>5.0</v>
+        <v>237</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N37" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P37" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="Q37" s="2">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="R37" s="2">
         <v>5.0</v>
@@ -4197,13 +4275,13 @@
       <c r="S37" s="2">
         <v>5.0</v>
       </c>
-      <c r="T37" s="2"/>
+      <c r="T37" s="2" t="s">
+        <v>238</v>
+      </c>
       <c r="U37" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V37" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="V37" s="2"/>
       <c r="W37" s="3"/>
       <c r="X37" s="3"/>
       <c r="Y37" s="3"/>
@@ -4212,10 +4290,10 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>29</v>
@@ -4224,59 +4302,57 @@
         <v>30</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="I38" s="2">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M38" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>37</v>
+        <v>243</v>
+      </c>
+      <c r="K38" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L38" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M38" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N38" s="2">
+        <v>5.0</v>
       </c>
       <c r="O38" s="2">
         <v>5.0</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q38" s="2">
+      <c r="P38" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R38" s="2">
         <v>3.0</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="S38" s="2">
         <v>5.0</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="U38" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V38" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="V38" s="2"/>
       <c r="W38" s="3"/>
       <c r="X38" s="3"/>
       <c r="Y38" s="3"/>
@@ -4285,10 +4361,10 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>29</v>
@@ -4297,59 +4373,57 @@
         <v>30</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>35</v>
+        <v>248</v>
+      </c>
+      <c r="I39" s="2">
+        <v>6.0</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>37</v>
+        <v>249</v>
+      </c>
+      <c r="K39" s="2">
+        <v>4.0</v>
       </c>
       <c r="L39" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M39" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="N39" s="2" t="s">
-        <v>37</v>
+        <v>4.0</v>
+      </c>
+      <c r="M39" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="N39" s="2">
+        <v>4.0</v>
       </c>
       <c r="O39" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P39" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q39" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="R39" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="S39" s="2" t="s">
-        <v>37</v>
+        <v>4.0</v>
+      </c>
+      <c r="P39" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="Q39" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="R39" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="S39" s="2">
+        <v>4.0</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="U39" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="V39" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="V39" s="2"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
@@ -4358,10 +4432,10 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>29</v>
@@ -4370,57 +4444,55 @@
         <v>30</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>35</v>
+        <v>254</v>
+      </c>
+      <c r="I40" s="2">
+        <v>8.0</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="L40" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M40" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="N40" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O40" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="P40" s="2" t="s">
-        <v>37</v>
+      <c r="L40" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="M40" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="N40" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="O40" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="P40" s="2">
+        <v>2.0</v>
       </c>
       <c r="Q40" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="R40" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="S40" s="2">
         <v>5.0</v>
       </c>
       <c r="T40" s="2"/>
       <c r="U40" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V40" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="V40" s="2"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
@@ -4429,10 +4501,10 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>29</v>
@@ -4441,59 +4513,57 @@
         <v>30</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G41" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="I41" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="J41" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="H41" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="I41" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>257</v>
-      </c>
       <c r="K41" s="2">
         <v>5.0</v>
       </c>
-      <c r="L41" s="2" t="s">
+      <c r="L41" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="M41" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N41" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M41" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="N41" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O41" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P41" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q41" s="2" t="s">
-        <v>38</v>
+      <c r="O41" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P41" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="Q41" s="2">
+        <v>4.0</v>
       </c>
       <c r="R41" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S41" s="2">
-        <v>4.0</v>
+        <v>3.0</v>
+      </c>
+      <c r="S41" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="U41" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="V41" s="2" t="s">
-        <v>148</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="V41" s="2"/>
       <c r="W41" s="3"/>
       <c r="X41" s="3"/>
       <c r="Y41" s="3"/>
@@ -4502,10 +4572,10 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>29</v>
@@ -4514,57 +4584,55 @@
         <v>30</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I42" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="K42" s="2">
         <v>5.0</v>
       </c>
       <c r="L42" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="M42" s="2">
         <v>3.0</v>
       </c>
+      <c r="M42" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="N42" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="O42" s="2" t="s">
-        <v>37</v>
+        <v>5.0</v>
+      </c>
+      <c r="O42" s="2">
+        <v>5.0</v>
       </c>
       <c r="P42" s="2">
         <v>5.0</v>
       </c>
-      <c r="Q42" s="2" t="s">
-        <v>38</v>
+      <c r="Q42" s="2">
+        <v>5.0</v>
       </c>
       <c r="R42" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="S42" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="T42" s="2"/>
       <c r="U42" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="V42" s="2" t="s">
-        <v>47</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="V42" s="2"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
       <c r="Y42" s="3"/>
@@ -4573,10 +4641,10 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>29</v>
@@ -4585,59 +4653,55 @@
         <v>30</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="I43" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="K43" s="2" t="s">
-        <v>37</v>
+        <v>270</v>
+      </c>
+      <c r="K43" s="2">
+        <v>5.0</v>
       </c>
       <c r="L43" s="2">
         <v>5.0</v>
       </c>
-      <c r="M43" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="N43" s="2" t="s">
-        <v>37</v>
+      <c r="M43" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N43" s="2">
+        <v>5.0</v>
       </c>
       <c r="O43" s="2">
         <v>5.0</v>
       </c>
       <c r="P43" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="Q43" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="R43" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="S43" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="T43" s="2" t="s">
-        <v>269</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="T43" s="2"/>
       <c r="U43" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="V43" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="V43" s="2"/>
       <c r="W43" s="3"/>
       <c r="X43" s="3"/>
       <c r="Y43" s="3"/>
@@ -4646,10 +4710,10 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>29</v>
@@ -4658,25 +4722,25 @@
         <v>30</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="K44" s="2">
-        <v>5.0</v>
+        <v>275</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>37</v>
@@ -4684,8 +4748,8 @@
       <c r="M44" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="N44" s="2">
-        <v>5.0</v>
+      <c r="N44" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="O44" s="2" t="s">
         <v>37</v>
@@ -4696,19 +4760,19 @@
       <c r="Q44" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="R44" s="2">
-        <v>4.0</v>
+      <c r="R44" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="S44" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="T44" s="2"/>
+      <c r="T44" s="2" t="s">
+        <v>276</v>
+      </c>
       <c r="U44" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="V44" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V44" s="2"/>
       <c r="W44" s="3"/>
       <c r="X44" s="3"/>
       <c r="Y44" s="3"/>
@@ -4717,10 +4781,10 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>29</v>
@@ -4729,28 +4793,28 @@
         <v>30</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="I45" s="2">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="K45" s="2">
         <v>5.0</v>
       </c>
-      <c r="L45" s="2" t="s">
-        <v>37</v>
+      <c r="L45" s="2">
+        <v>5.0</v>
       </c>
       <c r="M45" s="2">
         <v>5.0</v>
@@ -4758,28 +4822,26 @@
       <c r="N45" s="2">
         <v>5.0</v>
       </c>
-      <c r="O45" s="2" t="s">
-        <v>37</v>
+      <c r="O45" s="2">
+        <v>5.0</v>
       </c>
       <c r="P45" s="2">
         <v>5.0</v>
       </c>
       <c r="Q45" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="R45" s="2">
         <v>5.0</v>
       </c>
       <c r="S45" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="T45" s="2"/>
       <c r="U45" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="V45" s="2" t="s">
-        <v>148</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V45" s="2"/>
       <c r="W45" s="3"/>
       <c r="X45" s="3"/>
       <c r="Y45" s="3"/>
@@ -4788,10 +4850,10 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>29</v>
@@ -4800,22 +4862,22 @@
         <v>30</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>35</v>
+        <v>285</v>
+      </c>
+      <c r="I46" s="2">
+        <v>9.0</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>37</v>
@@ -4829,30 +4891,28 @@
       <c r="N46" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="O46" s="2" t="s">
-        <v>37</v>
+      <c r="O46" s="2">
+        <v>5.0</v>
       </c>
       <c r="P46" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="Q46" s="2" t="s">
-        <v>37</v>
+      <c r="Q46" s="2">
+        <v>3.0</v>
       </c>
       <c r="R46" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="S46" s="2" t="s">
-        <v>37</v>
+      <c r="S46" s="2">
+        <v>5.0</v>
       </c>
       <c r="T46" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="U46" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V46" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V46" s="2"/>
       <c r="W46" s="3"/>
       <c r="X46" s="3"/>
       <c r="Y46" s="3"/>
@@ -4861,7 +4921,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>28</v>
@@ -4873,57 +4933,57 @@
         <v>30</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I47" s="2">
-        <v>6.0</v>
+        <v>291</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="K47" s="2">
-        <v>5.0</v>
+        <v>292</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="L47" s="2">
         <v>5.0</v>
       </c>
-      <c r="M47" s="2">
-        <v>3.0</v>
+      <c r="M47" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="O47" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
+      </c>
+      <c r="O47" s="2">
+        <v>5.0</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q47" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="R47" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="S47" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="T47" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="Q47" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R47" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S47" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T47" s="2" t="s">
+        <v>293</v>
+      </c>
       <c r="U47" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V47" s="2" t="s">
-        <v>148</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V47" s="2"/>
       <c r="W47" s="3"/>
       <c r="X47" s="3"/>
       <c r="Y47" s="3"/>
@@ -4932,10 +4992,10 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>29</v>
@@ -4944,43 +5004,43 @@
         <v>30</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="I48" s="2">
-        <v>9.0</v>
+        <v>297</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="K48" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L48" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M48" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N48" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O48" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P48" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q48" s="2" t="s">
-        <v>37</v>
+        <v>298</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N48" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O48" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P48" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q48" s="2">
+        <v>5.0</v>
       </c>
       <c r="R48" s="2">
         <v>5.0</v>
@@ -4990,11 +5050,9 @@
       </c>
       <c r="T48" s="2"/>
       <c r="U48" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V48" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V48" s="2"/>
       <c r="W48" s="3"/>
       <c r="X48" s="3"/>
       <c r="Y48" s="3"/>
@@ -5003,7 +5061,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>28</v>
@@ -5015,59 +5073,57 @@
         <v>30</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="I49" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="K49" s="2" t="s">
-        <v>38</v>
+        <v>303</v>
+      </c>
+      <c r="K49" s="2">
+        <v>5.0</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M49" s="2" t="s">
+      <c r="M49" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="N49" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O49" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P49" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N49" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="O49" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="P49" s="2">
-        <v>3.0</v>
-      </c>
       <c r="Q49" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="R49" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="S49" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R49" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S49" s="2">
+        <v>4.0</v>
       </c>
       <c r="T49" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="U49" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V49" s="2" t="s">
-        <v>148</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="V49" s="2"/>
       <c r="W49" s="3"/>
       <c r="X49" s="3"/>
       <c r="Y49" s="3"/>
@@ -5076,7 +5132,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>28</v>
@@ -5088,59 +5144,55 @@
         <v>30</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="I50" s="2" t="s">
-        <v>35</v>
+        <v>308</v>
+      </c>
+      <c r="I50" s="2">
+        <v>7.0</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="K50" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L50" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M50" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="N50" s="2" t="s">
-        <v>37</v>
+        <v>309</v>
+      </c>
+      <c r="K50" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L50" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="M50" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N50" s="2">
+        <v>3.0</v>
       </c>
       <c r="O50" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="P50" s="2" t="s">
-        <v>37</v>
+      <c r="P50" s="2">
+        <v>5.0</v>
       </c>
       <c r="Q50" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="R50" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="S50" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="T50" s="2" t="s">
-        <v>307</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="R50" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S50" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T50" s="2"/>
       <c r="U50" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V50" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="V50" s="2"/>
       <c r="W50" s="3"/>
       <c r="X50" s="3"/>
       <c r="Y50" s="3"/>
@@ -5149,7 +5201,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>28</v>
@@ -5161,28 +5213,28 @@
         <v>30</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>35</v>
+        <v>313</v>
+      </c>
+      <c r="I51" s="2">
+        <v>8.0</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="L51" s="2" t="s">
-        <v>37</v>
+      <c r="L51" s="2">
+        <v>5.0</v>
       </c>
       <c r="M51" s="2" t="s">
         <v>37</v>
@@ -5190,28 +5242,28 @@
       <c r="N51" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="O51" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="P51" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q51" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="R51" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="S51" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="T51" s="2"/>
+      <c r="O51" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P51" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="Q51" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="R51" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="S51" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="T51" s="2" t="s">
+        <v>315</v>
+      </c>
       <c r="U51" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V51" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="V51" s="2"/>
       <c r="W51" s="3"/>
       <c r="X51" s="3"/>
       <c r="Y51" s="3"/>
@@ -5220,7 +5272,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>28</v>
@@ -5232,59 +5284,55 @@
         <v>30</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="I52" s="2">
-        <v>8.0</v>
+        <v>319</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="K52" s="2">
         <v>5.0</v>
       </c>
-      <c r="L52" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="M52" s="2">
-        <v>4.0</v>
+      <c r="L52" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M52" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="N52" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="O52" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="P52" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q52" s="2">
-        <v>5.0</v>
+        <v>5.0</v>
+      </c>
+      <c r="O52" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P52" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q52" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="R52" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S52" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="T52" s="2" t="s">
-        <v>318</v>
-      </c>
+        <v>4.0</v>
+      </c>
+      <c r="S52" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T52" s="2"/>
       <c r="U52" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V52" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="V52" s="2"/>
       <c r="W52" s="3"/>
       <c r="X52" s="3"/>
       <c r="Y52" s="3"/>
@@ -5293,7 +5341,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>28</v>
@@ -5305,59 +5353,55 @@
         <v>30</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="I53" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K53" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="L53" s="2">
-        <v>5.0</v>
+        <v>5.0</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="M53" s="2">
         <v>5.0</v>
       </c>
       <c r="N53" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="O53" s="2">
-        <v>2.0</v>
+        <v>5.0</v>
+      </c>
+      <c r="O53" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P53" s="2">
         <v>5.0</v>
       </c>
       <c r="Q53" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="R53" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="S53" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="T53" s="2" t="s">
-        <v>324</v>
-      </c>
+        <v>4.0</v>
+      </c>
+      <c r="T53" s="2"/>
       <c r="U53" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V53" s="2" t="s">
-        <v>47</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="V53" s="2"/>
       <c r="W53" s="3"/>
       <c r="X53" s="3"/>
       <c r="Y53" s="3"/>
@@ -5366,10 +5410,10 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>29</v>
@@ -5378,22 +5422,22 @@
         <v>30</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K54" s="2" t="s">
         <v>37</v>
@@ -5422,13 +5466,13 @@
       <c r="S54" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="T54" s="2"/>
+      <c r="T54" s="2" t="s">
+        <v>331</v>
+      </c>
       <c r="U54" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V54" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V54" s="2"/>
       <c r="W54" s="3"/>
       <c r="X54" s="3"/>
       <c r="Y54" s="3"/>
@@ -5437,10 +5481,10 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>29</v>
@@ -5449,22 +5493,22 @@
         <v>30</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="I55" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="K55" s="2">
         <v>5.0</v>
@@ -5473,33 +5517,31 @@
         <v>5.0</v>
       </c>
       <c r="M55" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q55" s="2">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="R55" s="2">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="S55" s="2">
         <v>4.0</v>
       </c>
       <c r="T55" s="2"/>
       <c r="U55" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="V55" s="2" t="s">
-        <v>47</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="V55" s="2"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
@@ -5508,10 +5550,10 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>29</v>
@@ -5520,57 +5562,55 @@
         <v>30</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="I56" s="2" t="s">
-        <v>35</v>
+        <v>340</v>
+      </c>
+      <c r="I56" s="2">
+        <v>9.0</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="K56" s="2">
         <v>5.0</v>
       </c>
-      <c r="L56" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M56" s="2" t="s">
-        <v>37</v>
+      <c r="L56" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M56" s="2">
+        <v>5.0</v>
       </c>
       <c r="N56" s="2">
         <v>5.0</v>
       </c>
-      <c r="O56" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="P56" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q56" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="R56" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="S56" s="2" t="s">
-        <v>37</v>
+      <c r="O56" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P56" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q56" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R56" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S56" s="2">
+        <v>5.0</v>
       </c>
       <c r="T56" s="2"/>
       <c r="U56" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="V56" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V56" s="2"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
@@ -5579,10 +5619,10 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>29</v>
@@ -5591,59 +5631,57 @@
         <v>30</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="I57" s="2">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="K57" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L57" s="2">
+        <v>346</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M57" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N57" s="2">
         <v>2.0</v>
       </c>
-      <c r="M57" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N57" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="O57" s="2" t="s">
-        <v>37</v>
+      <c r="O57" s="2">
+        <v>3.0</v>
       </c>
       <c r="P57" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="Q57" s="2">
         <v>3.0</v>
       </c>
-      <c r="R57" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S57" s="2">
-        <v>5.0</v>
+      <c r="Q57" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R57" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S57" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="T57" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="U57" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="V57" s="2" t="s">
-        <v>47</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="V57" s="2"/>
       <c r="W57" s="3"/>
       <c r="X57" s="3"/>
       <c r="Y57" s="3"/>
@@ -5652,10 +5690,10 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>29</v>
@@ -5664,59 +5702,57 @@
         <v>30</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="I58" s="2">
-        <v>9.0</v>
+        <v>351</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="K58" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="L58" s="2">
-        <v>5.0</v>
+        <v>352</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L58" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="M58" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="N58" s="2">
-        <v>5.0</v>
+      <c r="N58" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="O58" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="P58" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="Q58" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="R58" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="S58" s="2">
-        <v>5.0</v>
+      <c r="P58" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q58" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R58" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S58" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="T58" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="U58" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="V58" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V58" s="2"/>
       <c r="W58" s="3"/>
       <c r="X58" s="3"/>
       <c r="Y58" s="3"/>
@@ -5725,10 +5761,10 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>29</v>
@@ -5737,22 +5773,22 @@
         <v>30</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K59" s="2" t="s">
         <v>37</v>
@@ -5760,8 +5796,8 @@
       <c r="L59" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="M59" s="2">
-        <v>5.0</v>
+      <c r="M59" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="N59" s="2" t="s">
         <v>37</v>
@@ -5772,22 +5808,20 @@
       <c r="P59" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="Q59" s="2">
-        <v>3.0</v>
+      <c r="Q59" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="R59" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="S59" s="2">
-        <v>5.0</v>
+      <c r="S59" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="T59" s="2"/>
       <c r="U59" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V59" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V59" s="2"/>
       <c r="W59" s="3"/>
       <c r="X59" s="3"/>
       <c r="Y59" s="3"/>
@@ -5796,10 +5830,10 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>29</v>
@@ -5808,37 +5842,37 @@
         <v>30</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I60" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K60" s="2">
         <v>5.0</v>
       </c>
       <c r="L60" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="M60" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="N60" s="2">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="O60" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="P60" s="2">
         <v>5.0</v>
@@ -5853,14 +5887,12 @@
         <v>5.0</v>
       </c>
       <c r="T60" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="U60" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V60" s="2" t="s">
-        <v>47</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="V60" s="2"/>
       <c r="W60" s="3"/>
       <c r="X60" s="3"/>
       <c r="Y60" s="3"/>
@@ -5869,10 +5901,10 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>29</v>
@@ -5881,59 +5913,57 @@
         <v>30</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="I61" s="2" t="s">
-        <v>35</v>
+        <v>368</v>
+      </c>
+      <c r="I61" s="2">
+        <v>8.0</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="K61" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L61" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M61" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="N61" s="2" t="s">
-        <v>37</v>
+        <v>369</v>
+      </c>
+      <c r="K61" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="L61" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M61" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N61" s="2">
+        <v>2.0</v>
       </c>
       <c r="O61" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P61" s="2" t="s">
-        <v>37</v>
+        <v>2.0</v>
+      </c>
+      <c r="P61" s="2">
+        <v>5.0</v>
       </c>
       <c r="Q61" s="2">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="R61" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="S61" s="2" t="s">
-        <v>37</v>
+        <v>4.0</v>
+      </c>
+      <c r="S61" s="2">
+        <v>5.0</v>
       </c>
       <c r="T61" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="U61" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V61" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="V61" s="2"/>
       <c r="W61" s="3"/>
       <c r="X61" s="3"/>
       <c r="Y61" s="3"/>
@@ -5942,10 +5972,10 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>29</v>
@@ -5954,22 +5984,22 @@
         <v>30</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="I62" s="2">
-        <v>9.0</v>
+        <v>374</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="K62" s="2" t="s">
         <v>37</v>
@@ -5992,19 +6022,17 @@
       <c r="Q62" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="R62" s="2">
-        <v>5.0</v>
+      <c r="R62" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="S62" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="T62" s="3"/>
+      <c r="T62" s="2"/>
       <c r="U62" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V62" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V62" s="2"/>
       <c r="W62" s="3"/>
       <c r="X62" s="3"/>
       <c r="Y62" s="3"/>
@@ -6013,7 +6041,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>28</v>
@@ -6025,59 +6053,55 @@
         <v>30</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="I63" s="2">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="K63" s="2" t="s">
-        <v>37</v>
+        <v>380</v>
+      </c>
+      <c r="K63" s="2">
+        <v>5.0</v>
       </c>
       <c r="L63" s="2">
         <v>5.0</v>
       </c>
       <c r="M63" s="2">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="N63" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="O63" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="P63" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q63" s="2" t="s">
-        <v>37</v>
+      <c r="O63" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P63" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q63" s="2">
+        <v>2.0</v>
       </c>
       <c r="R63" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S63" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="T63" s="2" t="s">
-        <v>379</v>
-      </c>
+        <v>2.0</v>
+      </c>
+      <c r="S63" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="T63" s="2"/>
       <c r="U63" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V63" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="V63" s="2"/>
       <c r="W63" s="3"/>
       <c r="X63" s="3"/>
       <c r="Y63" s="3"/>
@@ -6086,7 +6110,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>28</v>
@@ -6098,34 +6122,34 @@
         <v>30</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="I64" s="2">
-        <v>8.0</v>
+        <v>384</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="K64" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="L64" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="M64" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="N64" s="2" t="s">
-        <v>37</v>
+      <c r="M64" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N64" s="2">
+        <v>5.0</v>
       </c>
       <c r="O64" s="2" t="s">
         <v>37</v>
@@ -6134,21 +6158,19 @@
         <v>37</v>
       </c>
       <c r="Q64" s="2">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="R64" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="S64" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="T64" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="S64" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T64" s="2"/>
       <c r="U64" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V64" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="V64" s="2"/>
       <c r="W64" s="3"/>
       <c r="X64" s="3"/>
       <c r="Y64" s="3"/>
@@ -6157,7 +6179,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>28</v>
@@ -6169,57 +6191,57 @@
         <v>30</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="I65" s="2" t="s">
-        <v>35</v>
+        <v>389</v>
+      </c>
+      <c r="I65" s="2">
+        <v>8.0</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="K65" s="2">
         <v>5.0</v>
       </c>
-      <c r="L65" s="2" t="s">
-        <v>37</v>
+      <c r="L65" s="2">
+        <v>2.0</v>
       </c>
       <c r="M65" s="2">
         <v>5.0</v>
       </c>
       <c r="N65" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O65" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P65" s="2" t="s">
-        <v>37</v>
+        <v>4.0</v>
+      </c>
+      <c r="O65" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P65" s="2">
+        <v>4.0</v>
       </c>
       <c r="Q65" s="2">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="R65" s="2">
         <v>5.0</v>
       </c>
-      <c r="S65" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="T65" s="3"/>
+      <c r="S65" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T65" s="2" t="s">
+        <v>391</v>
+      </c>
       <c r="U65" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V65" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="V65" s="2"/>
       <c r="W65" s="3"/>
       <c r="X65" s="3"/>
       <c r="Y65" s="3"/>
@@ -6228,7 +6250,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>28</v>
@@ -6240,65 +6262,618 @@
         <v>30</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="I66" s="2" t="s">
-        <v>35</v>
+        <v>395</v>
+      </c>
+      <c r="I66" s="2">
+        <v>9.0</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K66" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="L66" s="2">
         <v>5.0</v>
       </c>
-      <c r="M66" s="2">
-        <v>5.0</v>
+      <c r="M66" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="N66" s="2">
         <v>5.0</v>
       </c>
-      <c r="O66" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P66" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q66" s="2" t="s">
-        <v>37</v>
+      <c r="O66" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P66" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="Q66" s="2">
+        <v>2.0</v>
       </c>
       <c r="R66" s="2">
         <v>4.0</v>
       </c>
       <c r="S66" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="T66" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="U66" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V66" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="V66" s="2"/>
       <c r="W66" s="3"/>
       <c r="X66" s="3"/>
       <c r="Y66" s="3"/>
       <c r="Z66" s="3"/>
       <c r="AA66" s="3"/>
     </row>
+    <row r="67">
+      <c r="A67" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M67" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N67" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O67" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P67" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q67" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="R67" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S67" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T67" s="2"/>
+      <c r="U67" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="V67" s="2"/>
+      <c r="W67" s="3"/>
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+      <c r="Z67" s="3"/>
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="I68" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="K68" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L68" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M68" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N68" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O68" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P68" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q68" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R68" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S68" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T68" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="U68" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="V68" s="2"/>
+      <c r="W68" s="3"/>
+      <c r="X68" s="3"/>
+      <c r="Y68" s="3"/>
+      <c r="Z68" s="3"/>
+      <c r="AA68" s="3"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L69" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M69" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N69" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O69" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P69" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q69" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="R69" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="S69" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T69" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="U69" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="V69" s="2"/>
+      <c r="W69" s="3"/>
+      <c r="X69" s="3"/>
+      <c r="Y69" s="3"/>
+      <c r="Z69" s="3"/>
+      <c r="AA69" s="3"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="I70" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L70" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M70" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N70" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O70" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P70" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q70" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R70" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S70" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T70" s="2"/>
+      <c r="U70" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="V70" s="3"/>
+      <c r="W70" s="3"/>
+      <c r="X70" s="3"/>
+      <c r="Y70" s="3"/>
+      <c r="Z70" s="3"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="I71" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="K71" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L71" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M71" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="N71" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O71" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="P71" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q71" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R71" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S71" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T71" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="U71" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="V71" s="3"/>
+      <c r="W71" s="3"/>
+      <c r="X71" s="3"/>
+      <c r="Y71" s="3"/>
+      <c r="Z71" s="3"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="I72" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="K72" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M72" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="N72" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O72" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P72" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q72" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R72" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S72" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T72" s="2"/>
+      <c r="U72" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="V72" s="3"/>
+      <c r="W72" s="3"/>
+      <c r="X72" s="3"/>
+      <c r="Y72" s="3"/>
+      <c r="Z72" s="3"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="K73" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L73" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M73" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N73" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O73" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P73" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q73" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R73" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S73" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T73" s="2"/>
+      <c r="U73" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="V73" s="3"/>
+      <c r="W73" s="3"/>
+      <c r="X73" s="3"/>
+      <c r="Y73" s="3"/>
+      <c r="Z73" s="3"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="K74" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L74" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M74" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N74" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O74" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P74" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q74" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R74" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="S74" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="T74" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="U74" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="V74" s="3"/>
+      <c r="W74" s="3"/>
+      <c r="X74" s="3"/>
+      <c r="Y74" s="3"/>
+      <c r="Z74" s="3"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
